--- a/docs/collections/agriculture/metadata/data.xlsx
+++ b/docs/collections/agriculture/metadata/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG36"/>
+  <dimension ref="A1:AH36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,145 +439,150 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>出版者</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>刊行年、書写年等</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>冊数</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>請求記号</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>注記</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>異なりアクセスタイトル</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>解説URL</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>＜日本語＞コレクション名</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>＜英語＞コレクション名</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>巻号</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Series Alternative</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>iiif viewer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>ウェブサイトURL</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>アイテムURL</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>利用条件</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>サムネイル</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>機械可読ドキュメント</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>帰属</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>viewingDirection</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>viewingHint</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>コレクション</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>ソート用項目</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>西暦</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>IIIFマニフェストURI</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>IIIF Search API URI</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>アノテーション付きIIIFマニフェストURI</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Link to TAPAS Project</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Text with Rich Text Format</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t># of media</t>
         </is>
@@ -606,145 +611,150 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>dcterms:publisher</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>dcterms:date</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>dcterms:extent</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>dcndl:callNumber</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>dcterms:description</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>dcndl:alternative</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>archiveshub:note</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>dcndl:seriesTitle</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>dcndl:seriesTitleTranscription</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>dcndl:volume</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>dcndl:seriesAlternative</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>iiif viewer</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>bibo:identifier</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>dcterms:isPartOf</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>dcterms:relation</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>dcterms:rights</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>foaf:thumbnail</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>rdfs:seeAlso</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>sc:attributionLabel</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>sc:viewingDirection</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>sc:viewingHint</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>uterms:databaseLabel</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>uterms:sort</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>uterms:year</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>uterms:manifestUri</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>uterms:searchApiUri</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>uterms:annotedManifest</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>uterms:linkToTapas</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>uterms:rtf</t>
         </is>
       </c>
-      <c r="AG2" t="n">
+      <c r="AH2" t="n">
         <v>2196</v>
       </c>
     </row>
@@ -769,22 +779,23 @@
           <t>河東牧童甯直麿 [画]</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
         <is>
           <t>安永7 [1778]</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>1軸</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>和:7</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>写本、巻子本、彩色図版
 書名は題簽による
@@ -793,96 +804,96 @@
 印記: 「游戯三昧院」,「文珠庵印」</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>http://www.lib.a.u-tokyo.ac.jp/tenji/125/04.html</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
         <is>
           <t>University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d9115c2c-6c49-1f2b-515e-c67ea4332ab9.json</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>d9115c2c-6c49-1f2b-515e-c67ea4332ab9</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/d9115c2c-6c49-1f2b-515e-c67ea4332ab9</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a854fb44d17ab0f9f5bd95a2637c311ae0149a3a.jpg</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/275040</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr">
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the
 University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr">
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d9115c2c-6c49-1f2b-515e-c67ea4332ab9/manifest</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="n">
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="n">
         <v>13</v>
       </c>
     </row>
@@ -907,116 +918,117 @@
           <t>[東京帝國大學農學部]</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
         <is>
           <t>[大正11(1922)]</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>地図1枚 +付図1枚</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>和:26</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>縮尺: 1:600
 書名上部に"東京府荏原郡目黒村、世田谷村豊多摩郡代々幡町、澁谷町"とあり</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>東京帝国大学農学部建物位置図 : 大正11年4月1日現在</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
         <is>
           <t>University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6d032fb5-0a2f-6e04-9e3c-6bb5f604714f.json</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>6d032fb5-0a2f-6e04-9e3c-6bb5f604714f</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/6d032fb5-0a2f-6e04-9e3c-6bb5f604714f</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ce5758680ca575da5f3a2c7c1a4efb30ec0575e9.jpg</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/275041</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr">
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr">
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6d032fb5-0a2f-6e04-9e3c-6bb5f604714f/manifest</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="n">
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="n">
         <v>29</v>
       </c>
     </row>
@@ -1041,115 +1053,116 @@
           <t>[東京帝國大學]</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
         <is>
           <t>[昭和12(1937)]</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>地図1枚</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>和:27</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>枠外に"東京印刷株式會社印売"とあり</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>東京帝国大学本部構内及農学部建物鳥瞰図 : 昭和12年6月30日現在</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
         <is>
           <t>University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/187cc82d-11e6-9912-9dd4-b4cca9b10970.json</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>187cc82d-11e6-9912-9dd4-b4cca9b10970</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/187cc82d-11e6-9912-9dd4-b4cca9b10970</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1ba32e3f0ffc84f504e4cc1d53c7cfe7bc88d7db.jpg</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/275042</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr">
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>003</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr">
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/187cc82d-11e6-9912-9dd4-b4cca9b10970/manifest</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="n">
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1170,99 +1183,100 @@
           <t>佐々木忠次郎 [著]</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
         <is>
           <t>大正7年(1918)12月序</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
         <is>
           <t>630:90:1</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
         <is>
           <t>University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3e6f484d-a4e0-7073-4365-b287924d423a.json</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>3e6f484d-a4e0-7073-4365-b287924d423a</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/3e6f484d-a4e0-7073-4365-b287924d423a</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/dfb6622529735856cf83a97769bb6837c181d6ff.jpg</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/439369</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr">
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>004</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr">
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3e6f484d-a4e0-7073-4365-b287924d423a/manifest</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="n">
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="n">
         <v>171</v>
       </c>
     </row>
@@ -1283,99 +1297,100 @@
           <t>佐々木忠次郎 [著]</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
         <is>
           <t>大正7年(1918)12月序</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
         <is>
           <t>630:90:2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
         <is>
           <t>University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f3bfde97-6dfb-3f09-33af-0c615a250268.json</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>f3bfde97-6dfb-3f09-33af-0c615a250268</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/f3bfde97-6dfb-3f09-33af-0c615a250268</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/32e2196c46703505110c06bdbf92fa9ad8ca481c.jpg</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/439370</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr">
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>005</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr">
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f3bfde97-6dfb-3f09-33af-0c615a250268/manifest</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="n">
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="n">
         <v>173</v>
       </c>
     </row>
@@ -1396,99 +1411,100 @@
           <t>佐々木忠次郎 [著]</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
         <is>
           <t>大正7年(1918)12月序</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
         <is>
           <t>630:90:3</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
         <is>
           <t>University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a09fc5f4-8edc-0d46-7340-e2768dbf7a05.json</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>a09fc5f4-8edc-0d46-7340-e2768dbf7a05</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/a09fc5f4-8edc-0d46-7340-e2768dbf7a05</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/67749c791401a4d15b01ec7720cf21569b4c7c67.jpg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/439371</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr">
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>006</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr">
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a09fc5f4-8edc-0d46-7340-e2768dbf7a05/manifest</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="n">
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="n">
         <v>178</v>
       </c>
     </row>
@@ -1509,99 +1525,100 @@
           <t>佐々木忠次郎 [著]</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
         <is>
           <t>大正7年(1918)12月序</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
         <is>
           <t>630:90:4</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
         <is>
           <t>University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9c79a3bb-34da-25bf-4243-4ba1709556a9.json</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>9c79a3bb-34da-25bf-4243-4ba1709556a9</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/9c79a3bb-34da-25bf-4243-4ba1709556a9</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a9c54d326cbc953cde434434eb26b6b81614129c.jpg</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/439372</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr">
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>007</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr">
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9c79a3bb-34da-25bf-4243-4ba1709556a9/manifest</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="n">
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="n">
         <v>142</v>
       </c>
     </row>
@@ -1622,99 +1639,100 @@
           <t>佐々木忠次郎 [著]</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
         <is>
           <t>大正7年(1918)12月序</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
         <is>
           <t>630:90:5</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
         <is>
           <t>University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/58f3ea6c-3626-9cbb-6cf8-33078f6e41bc.json</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>58f3ea6c-3626-9cbb-6cf8-33078f6e41bc</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/58f3ea6c-3626-9cbb-6cf8-33078f6e41bc</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/876c4079f5ebc054fab75c39ed25b18448581072.jpg</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/439373</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr">
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>008</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr">
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/58f3ea6c-3626-9cbb-6cf8-33078f6e41bc/manifest</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="n">
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="n">
         <v>145</v>
       </c>
     </row>
@@ -1735,99 +1753,100 @@
           <t>東京山林學校 [写]</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
         <is>
           <t>[明治期]</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>1冊</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>613:61</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b6e42779-162f-7bae-708c-bef438966890.json</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>b6e42779-162f-7bae-708c-bef438966890</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/b6e42779-162f-7bae-708c-bef438966890</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/14a8e8afeddd0ab3d4a4fd6cac5685bbab48346a.jpg</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/540593</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr">
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>009</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr">
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b6e42779-162f-7bae-708c-bef438966890/manifest</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="n">
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="n">
         <v>87</v>
       </c>
     </row>
@@ -1848,99 +1867,100 @@
           <t>東京山林學校 [写]</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
         <is>
           <t>[明治期]</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>1冊</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>613:62</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7a3e0c92-234b-1295-947b-d697d0d6955f.json</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>7a3e0c92-234b-1295-947b-d697d0d6955f</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/7a3e0c92-234b-1295-947b-d697d0d6955f</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/97c0529a040265b8bf2e67b949be578ed7e2d285.jpg</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/540592</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr">
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>010</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr">
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7a3e0c92-234b-1295-947b-d697d0d6955f/manifest</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="n">
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="n">
         <v>80</v>
       </c>
     </row>
@@ -1961,99 +1981,100 @@
           <t>[書写者不明]</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
         <is>
           <t>[明治期]</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>1冊</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>613:63</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/df8094b2-597f-5dcf-6c06-28af31a74c49.json</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>df8094b2-597f-5dcf-6c06-28af31a74c49</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/df8094b2-597f-5dcf-6c06-28af31a74c49</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/90f647a0bb13d794aef2957aa6c46c235205639d.jpg</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/540591</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr">
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>011</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr">
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/df8094b2-597f-5dcf-6c06-28af31a74c49/manifest</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="n">
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="n">
         <v>162</v>
       </c>
     </row>
@@ -2074,99 +2095,100 @@
           <t>池田次郎吉編</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
         <is>
           <t>1895年8月刊</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>1冊</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>613:44</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/627f6b5d-4e4c-81e1-7954-bd451f567a45.json</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>627f6b5d-4e4c-81e1-7954-bd451f567a45</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/627f6b5d-4e4c-81e1-7954-bd451f567a45</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3dc15e9dbabbc0158d9913d72e3e11b9ecf4f6f6.jpg</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/540590</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr">
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>012</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr">
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/627f6b5d-4e4c-81e1-7954-bd451f567a45/manifest</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="n">
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="n">
         <v>29</v>
       </c>
     </row>
@@ -2187,99 +2209,100 @@
           <t>[書写者不明]</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
         <is>
           <t>[書写年不明]</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>1冊</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>613:46</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b4814f58-5ae1-481d-0cfa-6938aa3a7620.json</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>b4814f58-5ae1-481d-0cfa-6938aa3a7620</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/b4814f58-5ae1-481d-0cfa-6938aa3a7620</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4fb75645c087af75f3055db0bb1e31fcfef680d6.jpg</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/540589</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr">
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="AA15" t="inlineStr">
         <is>
           <t>013</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr">
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b4814f58-5ae1-481d-0cfa-6938aa3a7620/manifest</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="n">
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="n">
         <v>50</v>
       </c>
     </row>
@@ -2300,99 +2323,100 @@
           <t>田中芳男, 小野職愨撰 ; 曲直瀬愛, 小森頼信校 ; 服部雪斎図画</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
         <is>
           <t>明治24[1891]年刊</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>1冊</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>613:29:1</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/87c1c4a4-9cce-5b5f-a5a4-ad58e2240372.json</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>87c1c4a4-9cce-5b5f-a5a4-ad58e2240372</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/87c1c4a4-9cce-5b5f-a5a4-ad58e2240372</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1cbe04ccda9c3a0604f3331dc0aea9527c04b140.jpg</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/540588</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr">
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="AA16" t="inlineStr">
         <is>
           <t>014</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr">
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/87c1c4a4-9cce-5b5f-a5a4-ad58e2240372/manifest</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="n">
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="n">
         <v>85</v>
       </c>
     </row>
@@ -2413,99 +2437,100 @@
           <t>田中芳男, 小野職愨撰 ; 曲直瀬愛, 小森頼信校 ; 服部雪斎図画</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
         <is>
           <t>明治24[1891]年刊</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>1冊</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>613:29:2</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/bb4b00b5-8a54-3698-656b-2b5baaa40938.json</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>bb4b00b5-8a54-3698-656b-2b5baaa40938</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/bb4b00b5-8a54-3698-656b-2b5baaa40938</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/5abde5eb843ebc906082579acb7b6b91347c34ad.jpg</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/540587</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr">
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="AA17" t="inlineStr">
         <is>
           <t>015</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr">
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/bb4b00b5-8a54-3698-656b-2b5baaa40938/manifest</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="n">
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="n">
         <v>78</v>
       </c>
     </row>
@@ -2526,99 +2551,100 @@
           <t>田中芳男, 小野職愨撰 ; 曲直瀬愛, 小森頼信校 ; 服部雪斎図画</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
         <is>
           <t>明治24[1891]年刊</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>1冊</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>613:29:3</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/42dfe305-0e6e-4d22-298a-d3895726a29a.json</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>42dfe305-0e6e-4d22-298a-d3895726a29a</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/42dfe305-0e6e-4d22-298a-d3895726a29a</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3364e66d4f25b6291d583e1b29042f5f25fc98e1.jpg</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/540586</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr">
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="AA18" t="inlineStr">
         <is>
           <t>016</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr">
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/42dfe305-0e6e-4d22-298a-d3895726a29a/manifest</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="n">
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="n">
         <v>71</v>
       </c>
     </row>
@@ -2639,99 +2665,100 @@
           <t>田中芳男, 小野職愨撰 ; 曲直瀬愛, 小森頼信校 ; 服部雪斎図画</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
         <is>
           <t>明治24[1891]年刊</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>1冊</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>613:29:4</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr">
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6041ed83-59e7-7bc0-196d-c7ed8d01673d.json</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>6041ed83-59e7-7bc0-196d-c7ed8d01673d</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/6041ed83-59e7-7bc0-196d-c7ed8d01673d</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0fd408ca8f01b4b48b70c80355fcf0e8b4f63d97.jpg</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/540585</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr">
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="AA19" t="inlineStr">
         <is>
           <t>017</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr">
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6041ed83-59e7-7bc0-196d-c7ed8d01673d/manifest</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="n">
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="n">
         <v>59</v>
       </c>
     </row>
@@ -2752,99 +2779,100 @@
           <t>田中芳男, 小野職愨撰 ; 曲直瀬愛, 小森頼信校 ; 服部雪斎図画</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
         <is>
           <t>明治24[1891]年刊</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>1冊</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>613:29:5</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr">
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/5bfde8bf-0b54-7848-97d6-1ee30cf9a645.json</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>5bfde8bf-0b54-7848-97d6-1ee30cf9a645</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/5bfde8bf-0b54-7848-97d6-1ee30cf9a645</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/bf05396c6209233d94c7883e25d8a4cf3624d93e.jpg</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/540584</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr">
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>018</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr">
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/5bfde8bf-0b54-7848-97d6-1ee30cf9a645/manifest</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="n">
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="n">
         <v>47</v>
       </c>
     </row>
@@ -2865,99 +2893,100 @@
           <t>田中芳男, 小野職愨撰 ; 曲直瀬愛, 小森頼信校 ; 服部雪斎図画</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
         <is>
           <t>明治24[1891]年刊</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>1冊</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>613:29:6</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7844f0c7-2434-7b74-15df-c74b0e3c8e38.json</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>7844f0c7-2434-7b74-15df-c74b0e3c8e38</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/7844f0c7-2434-7b74-15df-c74b0e3c8e38</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/64363d5cbfe12a51092e585f5f6f940ad29ec7e6.jpg</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/540583</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr">
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>019</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr">
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7844f0c7-2434-7b74-15df-c74b0e3c8e38/manifest</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr"/>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="n">
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="n">
         <v>46</v>
       </c>
     </row>
@@ -2978,99 +3007,100 @@
           <t>田中芳男, 小野職愨撰 ; 曲直瀬愛, 小森頼信校 ; 服部雪斎図画</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
         <is>
           <t>明治24[1891]年刊</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>1冊</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>613:29:7</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr">
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/29d63e58-754f-7565-a41a-29cc2d5e4e3e.json</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>29d63e58-754f-7565-a41a-29cc2d5e4e3e</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/29d63e58-754f-7565-a41a-29cc2d5e4e3e</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/28276688ee682e8065bd9bec5c8e77ad77cc8f53.jpg</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/540582</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr">
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="AA22" t="inlineStr">
         <is>
           <t>020</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr">
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/29d63e58-754f-7565-a41a-29cc2d5e4e3e/manifest</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="n">
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="n">
         <v>49</v>
       </c>
     </row>
@@ -3091,103 +3121,104 @@
           <t>農商務省山林局編纂</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
         <is>
           <t>1912</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>1冊</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>613.793:N77-N</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>[図版]</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr">
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c2466a42-0add-7f2b-7d11-58aaebea953f.json</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>c2466a42-0add-7f2b-7d11-58aaebea953f</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/c2466a42-0add-7f2b-7d11-58aaebea953f</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/101b027d6bc01f45b781ec4b1b5ade9e683fc0e2.jpg</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541553</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr">
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
+      <c r="AA23" t="inlineStr">
         <is>
           <t>021</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr">
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c2466a42-0add-7f2b-7d11-58aaebea953f/manifest</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="n">
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="n">
         <v>22</v>
       </c>
     </row>
@@ -3208,103 +3239,104 @@
           <t>白澤保美編著 ; 丸山宣光,大石榮雄畫</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
         <is>
           <t>1900-1908</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>1冊</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>650:21:1</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>第一秩</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr">
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/2c310bb0-6cb1-4f7b-2b7d-7d6255cf680e.json</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>2c310bb0-6cb1-4f7b-2b7d-7d6255cf680e</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/2c310bb0-6cb1-4f7b-2b7d-7d6255cf680e</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/83a4e1b5b89b77ef327aaabfe7ae54efcc673b83.jpg</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541552</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr">
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="AA24" t="inlineStr">
         <is>
           <t>022</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr">
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/2c310bb0-6cb1-4f7b-2b7d-7d6255cf680e/manifest</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="n">
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="n">
         <v>102</v>
       </c>
     </row>
@@ -3325,103 +3357,104 @@
           <t>白澤保美編著 ; 丸山宣光,大石榮雄畫</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
         <is>
           <t>1900-1908</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>1冊</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>650:21:2</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>第二秩</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr">
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/70f02bc2-6f66-84ec-3578-058a8d03668c.json</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>70f02bc2-6f66-84ec-3578-058a8d03668c</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/70f02bc2-6f66-84ec-3578-058a8d03668c</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f647534e44867cf617598f2d51e26d05643d0948.jpg</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541551</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr">
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>023</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr">
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/70f02bc2-6f66-84ec-3578-058a8d03668c/manifest</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="n">
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="n">
         <v>84</v>
       </c>
     </row>
@@ -3442,107 +3475,108 @@
           <t>農商務省山林局 [編纂]</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
         <is>
           <t>1912-1925</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>1冊</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>613.747:N77</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>奥付は第4集のもの。</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>第1~4集合冊</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f9dbea50-3d74-5d6e-03f2-b5bf339b5a2b.json</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>f9dbea50-3d74-5d6e-03f2-b5bf339b5a2b</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/f9dbea50-3d74-5d6e-03f2-b5bf339b5a2b</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/674d9cadf351cbd2facc9305e02d0769cbb9aa97.jpg</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541550</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr">
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
+      <c r="AA26" t="inlineStr">
         <is>
           <t>024</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr">
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f9dbea50-3d74-5d6e-03f2-b5bf339b5a2b/manifest</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="n">
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="n">
         <v>90</v>
       </c>
     </row>
@@ -3563,103 +3597,104 @@
           <t>和田英作,佐藤醇吉著</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
         <is>
           <t>1919-1920</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>1冊</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>613:87:1</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>第1輯第1編</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr">
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a2af6812-7fd8-2cf2-759d-11fff8990e95.json</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>a2af6812-7fd8-2cf2-759d-11fff8990e95</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/a2af6812-7fd8-2cf2-759d-11fff8990e95</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/79eddc772afeb6a83b0f3c57230c89b50848b7c2.jpg</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541549</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr">
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
+      <c r="AA27" t="inlineStr">
         <is>
           <t>025</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr">
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a2af6812-7fd8-2cf2-759d-11fff8990e95/manifest</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="n">
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="n">
         <v>22</v>
       </c>
     </row>
@@ -3680,103 +3715,104 @@
           <t>和田英作,佐藤醇吉著</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
         <is>
           <t>1919-1920</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>1冊</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>613:87:2</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>第1輯第2編</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/2da73342-76a3-0edc-8b07-d866f06d5ea3.json</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>2da73342-76a3-0edc-8b07-d866f06d5ea3</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/2da73342-76a3-0edc-8b07-d866f06d5ea3</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a25f6e6a6f3dc7075cf046171131e1dd30da1906.jpg</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541548</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr">
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
+      <c r="AA28" t="inlineStr">
         <is>
           <t>026</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr">
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/2da73342-76a3-0edc-8b07-d866f06d5ea3/manifest</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="n">
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="n">
         <v>21</v>
       </c>
     </row>
@@ -3797,103 +3833,104 @@
           <t>和田英作,佐藤醇吉著</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
         <is>
           <t>1919-1920</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>1冊</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>613:87:3</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>第1輯第3編</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr">
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e443b3ea-830a-907d-42a9-cb4036f27a96.json</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>e443b3ea-830a-907d-42a9-cb4036f27a96</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/e443b3ea-830a-907d-42a9-cb4036f27a96</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/6f34c6d2435321d152f7259e81741f4a89f6546b.jpg</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541547</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr">
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
+      <c r="AA29" t="inlineStr">
         <is>
           <t>027</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr">
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e443b3ea-830a-907d-42a9-cb4036f27a96/manifest</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr"/>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="n">
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="n">
         <v>20</v>
       </c>
     </row>
@@ -3914,103 +3951,104 @@
           <t>和田英作,佐藤醇吉著</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
         <is>
           <t>1919-1920</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>1冊</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>613:87:4</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>第1輯第4編</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr">
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8d83cc45-79ff-0188-659b-7ca5fd48849e.json</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>8d83cc45-79ff-0188-659b-7ca5fd48849e</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/8d83cc45-79ff-0188-659b-7ca5fd48849e</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/408216c089708be5af32f74482148d3a4efdd097.jpg</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541546</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr">
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
+      <c r="AA30" t="inlineStr">
         <is>
           <t>028</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr">
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8d83cc45-79ff-0188-659b-7ca5fd48849e/manifest</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="n">
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="n">
         <v>24</v>
       </c>
     </row>
@@ -4031,103 +4069,104 @@
           <t>和田英作,佐藤醇吉著</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
         <is>
           <t>1919-1920</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>1冊</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>613:87:5</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>第1輯第5編</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr">
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/30c60644-40b8-a0d3-9231-3b6320c7843e.json</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>30c60644-40b8-a0d3-9231-3b6320c7843e</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/30c60644-40b8-a0d3-9231-3b6320c7843e</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/03a77a3b6451aa20e1423800ecae92ce21c42553.jpg</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541545</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr">
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="AA31" t="inlineStr">
         <is>
           <t>029</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr">
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/30c60644-40b8-a0d3-9231-3b6320c7843e/manifest</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr"/>
-      <c r="AG31" t="n">
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="n">
         <v>22</v>
       </c>
     </row>
@@ -4148,103 +4187,104 @@
           <t>和田英作,佐藤醇吉著</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
         <is>
           <t>1919-1920</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>1冊</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>613:87:6</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>第1輯第6編</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/05fc859e-3db1-5c8b-323f-e11d3e9010cc.json</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>05fc859e-3db1-5c8b-323f-e11d3e9010cc</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/05fc859e-3db1-5c8b-323f-e11d3e9010cc</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b9e94c996c3c17fd669ef4fa8dffb81e33e9ac1b.jpg</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541544</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr">
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="AA32" t="inlineStr">
         <is>
           <t>030</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr">
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/05fc859e-3db1-5c8b-323f-e11d3e9010cc/manifest</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="n">
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="n">
         <v>20</v>
       </c>
     </row>
@@ -4265,103 +4305,104 @@
           <t>和田英作,佐藤醇吉著</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
         <is>
           <t>1919-1920</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>1冊</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>613:87:7</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>第1輯第7編</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0717b584-7f27-70c4-70e9-0dfc7ed28f77.json</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>0717b584-7f27-70c4-70e9-0dfc7ed28f77</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/0717b584-7f27-70c4-70e9-0dfc7ed28f77</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/6baf5a7867abd52890ddf2c0e298dde3871036fa.jpg</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541543</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr">
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="AA33" t="inlineStr">
         <is>
           <t>031</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr">
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0717b584-7f27-70c4-70e9-0dfc7ed28f77/manifest</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="n">
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="n">
         <v>20</v>
       </c>
     </row>
@@ -4382,103 +4423,104 @@
           <t>和田英作,佐藤醇吉著</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
         <is>
           <t>1919-1920</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>1冊</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>613:87:8</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>第1輯第8編</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4e17a945-4320-171d-142e-bd3838ba1cfa.json</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>4e17a945-4320-171d-142e-bd3838ba1cfa</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/4e17a945-4320-171d-142e-bd3838ba1cfa</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1534e0eaa9a76cbddc00ac2cf517eacce5f4bc43.jpg</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541542</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr">
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="AA34" t="inlineStr">
         <is>
           <t>032</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr"/>
-      <c r="AB34" t="inlineStr">
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4e17a945-4320-171d-142e-bd3838ba1cfa/manifest</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="n">
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="n">
         <v>21</v>
       </c>
     </row>
@@ -4499,107 +4541,108 @@
           <t>和田英作,佐藤醇吉著</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
         <is>
           <t>1919-1920</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>1冊</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>613:87:9</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>後半部分欠損</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>第1輯第9編</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr">
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/97a6ecb3-5cb2-08c3-0d4f-e057b8f2258b.json</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>97a6ecb3-5cb2-08c3-0d4f-e057b8f2258b</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/97a6ecb3-5cb2-08c3-0d4f-e057b8f2258b</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4338a576fa00a1b57f1dbf414ffeaed14fad4498.jpg</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541541</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr">
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="AA35" t="inlineStr">
         <is>
           <t>033</t>
         </is>
       </c>
-      <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr">
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/97a6ecb3-5cb2-08c3-0d4f-e057b8f2258b/manifest</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr"/>
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="n">
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4620,103 +4663,104 @@
           <t>和田英作,佐藤醇吉著</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
         <is>
           <t>1919-1920</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>1冊</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>613:87:10</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Agri. Library, UTokyo Collection</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>第1輯第10編</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr">
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c9f1ab4e-6bf9-997c-95a7-572c5e6b2597.json</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>c9f1ab4e-6bf9-997c-95a7-572c5e6b2597</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/c9f1ab4e-6bf9-997c-95a7-572c5e6b2597</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2c13ea887a4ea6f06c7e832e01a70527eeeb6617.jpg</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541540</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr">
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="AA36" t="inlineStr">
         <is>
           <t>034</t>
         </is>
       </c>
-      <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr">
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c9f1ab4e-6bf9-997c-95a7-572c5e6b2597/manifest</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr"/>
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="n">
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="n">
         <v>19</v>
       </c>
     </row>

--- a/docs/collections/agriculture/metadata/data.xlsx
+++ b/docs/collections/agriculture/metadata/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH36"/>
+  <dimension ref="A1:AH64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -755,7 +755,7 @@
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>2196</v>
+        <v>6773</v>
       </c>
     </row>
     <row r="3">
@@ -4764,6 +4764,3362 @@
         <v>19</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Castans' Lectures on agriculture</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>John Daniel Custance, 大内健[筆記]</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1878-1879</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>洋:86</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4e0dc54b-2d8a-7d80-2f37-40842b0ea589.json</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>4e0dc54b-2d8a-7d80-2f37-40842b0ea589</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/4e0dc54b-2d8a-7d80-2f37-40842b0ea589</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f654ef92709303ef6714617681b0d136403c1537.jpg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249154</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>035</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4e0dc54b-2d8a-7d80-2f37-40842b0ea589/manifest</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="n">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>E. Kinch's Lectures on chemistry, inorganic, with laboratory notes</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Edward Kinch, 大内健[筆記]</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1878-1880</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>洋:87:1</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/29e4da03-7e96-4dd2-68ba-f23004321f33.json</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>29e4da03-7e96-4dd2-68ba-f23004321f33</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/29e4da03-7e96-4dd2-68ba-f23004321f33</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/39b8badc7512534a6518ccfd07746632d4bb85c1.jpg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249156</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>036</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/29e4da03-7e96-4dd2-68ba-f23004321f33/manifest</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="n">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>E. Kinch's Lectures on chemistry, organic</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Edward Kinch, 大内健[筆記]</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1879-1880</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>洋:87:2</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f26d3e18-58ef-0ce5-8f74-ca48dfc99da0.json</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>f26d3e18-58ef-0ce5-8f74-ca48dfc99da0</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/f26d3e18-58ef-0ce5-8f74-ca48dfc99da0</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e9ef6f044676a534bb275bb8a09074bdd79b06e6.jpg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249157</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>037</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f26d3e18-58ef-0ce5-8f74-ca48dfc99da0/manifest</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="n">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>E. Kinch's Lectures on agricultural chemistry</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Edward Kinch, 大内健[筆記]</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1880-1881</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>洋:87:3</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/5a5250d3-95aa-066a-3a2e-1922bc793618.json</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>5a5250d3-95aa-066a-3a2e-1922bc793618</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/5a5250d3-95aa-066a-3a2e-1922bc793618</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/717ac355eec81f9adc4953d48a8d23e9bfe11d1b.jpg</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249155</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>038</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/5a5250d3-95aa-066a-3a2e-1922bc793618/manifest</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
+      <c r="AH40" t="n">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Results of analyse performed at the Chemical Laboratory of the Imperial College of Agriculture [1]</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Edward Kinch, Oskar Kellner, Y. Kozai</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1877-1905</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>洋:88:1</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>p. 1-181 by Edward Kinch, p.182- by Oskar Kellner</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d6210358-1b3e-2274-688f-08add7189baf.json</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>d6210358-1b3e-2274-688f-08add7189baf</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/d6210358-1b3e-2274-688f-08add7189baf</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4b7300af4b7d19dee9e9568a7b67af3098480e23.jpg</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249158</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>039</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d6210358-1b3e-2274-688f-08add7189baf/manifest</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="n">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Results of analyse performed at the Chemical Laboratory of the Imperial College of Agriculture [2]</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Edward Kinch, Oskar Kellner, Y. Kozai</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1877-1905</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>洋:88:2</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>almost by Y. Kozai</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4d74f571-9b2d-675f-0683-8a193cfe5e54.json</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>4d74f571-9b2d-675f-0683-8a193cfe5e54</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/4d74f571-9b2d-675f-0683-8a193cfe5e54</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3c1ae77ce4997a14770e524fa8d1cc6fd4245301.jpg</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249159</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>040</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4d74f571-9b2d-675f-0683-8a193cfe5e54/manifest</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Results of analyse performed at the Chemical Laboratory of the Imperial College of Agriculture [3], Analytical results, reported by students</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Edward Kinch, Oskar Kellner, Y. Kozai</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1877-1905</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>洋:88:3</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>reporeted by S. Muramatsu, T. Asano, N. Furukawa ... [et al.], partly in Japanese</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/44f9950d-5b3e-9234-19b6-c7b43c4509a0.json</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>44f9950d-5b3e-9234-19b6-c7b43c4509a0</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/44f9950d-5b3e-9234-19b6-c7b43c4509a0</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/07197f0c25e6af616ea5dedd6ac9a24fbf431adf.jpg</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249160</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>041</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/44f9950d-5b3e-9234-19b6-c7b43c4509a0/manifest</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>日本物産國盡 前篇巻之一(上)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>ニホン ブッサン クニズクシ ゼンペン</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>中島翠堂著 ; 中島仰山, 溝口月耕畫</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>鈴木喜右衞門</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1873.8</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>600:1:1</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>巻之一(上)</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7641f4d6-2186-27cb-a14b-5557175d5cff.json</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>7641f4d6-2186-27cb-a14b-5557175d5cff</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/7641f4d6-2186-27cb-a14b-5557175d5cff</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d2092dcb435163ecdbb4dd8a6dd9378acfb820b6.jpg</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249161</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>042</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7641f4d6-2186-27cb-a14b-5557175d5cff/manifest</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>日本物産國盡 前篇巻之二(中)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ニホン ブッサン クニズクシ ゼンペン</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>中島翠堂著 ; 中島仰山, 溝口月耕畫</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>鈴木喜右衞門</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>1873.8</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>600:1:2</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>巻之二(中)</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d46eb2e4-3308-8768-3c2c-c835345d4f16.json</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>d46eb2e4-3308-8768-3c2c-c835345d4f16</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/d46eb2e4-3308-8768-3c2c-c835345d4f16</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1e71e9250db867c3aa06c22c0c59903d16891138.jpg</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249162</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>043</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d46eb2e4-3308-8768-3c2c-c835345d4f16/manifest</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>日本物産國盡 前篇巻之三(下)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ニホン ブッサン クニズクシ ゼンペン</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>中島翠堂著 ; 中島仰山, 溝口月耕畫</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>鈴木喜右衞門</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1873.8</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>600:1:3</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>巻之三(下)</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/afc99ebe-2ecc-8868-360c-d0de65d61e98.json</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>afc99ebe-2ecc-8868-360c-d0de65d61e98</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/afc99ebe-2ecc-8868-360c-d0de65d61e98</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0fbc84dd2e140498a4cc78d031034a5d2412263b.jpg</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249163</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>044</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/afc99ebe-2ecc-8868-360c-d0de65d61e98/manifest</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
+      <c r="AH46" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>澳國博覽會報告書 [議院部 上-下]</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>オウコク ハクランカイ ホウコクショ ギインブ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>[澳国博覧会事務局]</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1875.8序</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>600:3:1</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>[議院部 上-下]</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1562ca02-6f67-313f-4f4e-14214acc7f40.json</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1562ca02-6f67-313f-4f4e-14214acc7f40</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/1562ca02-6f67-313f-4f4e-14214acc7f40</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/450226c5ec3d99e7a1cc07fc89c7752e8e67be35.jpg</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249164</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>045</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1562ca02-6f67-313f-4f4e-14214acc7f40/manifest</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
+      <c r="AH47" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>澳國博覽會報告書 礼法部</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>オウコク ハクランカイ ホウコクショ レイホウブ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>[澳国博覧会事務局]</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1875.8序</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>600:3:2</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>礼法部</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/00d56783-91e9-80a4-35b8-33f959a45063.json</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>00d56783-91e9-80a4-35b8-33f959a45063</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/00d56783-91e9-80a4-35b8-33f959a45063</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/6e5d14a047d82c524e04281e4a622f03f8f8f9d6.jpg</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249165</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>046</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/00d56783-91e9-80a4-35b8-33f959a45063/manifest</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
+      <c r="AH48" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>澳國博覽會報告書 博物館部 下</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>オウコク ハクランカイ ホウコクショ ハクブツカンブ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>[澳国博覧会事務局]</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1875.8序</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>600:3:3</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>博物館部 下</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/19dd4309-44fb-3da3-6648-2b8057719ca1.json</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>19dd4309-44fb-3da3-6648-2b8057719ca1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/19dd4309-44fb-3da3-6648-2b8057719ca1</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8e36e9cf933bce99e082ba384f4bc84c7fd702cd.jpg</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249166</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>047</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr"/>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/19dd4309-44fb-3da3-6648-2b8057719ca1/manifest</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
+      <c r="AH49" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>澳國博覽會報告書 道路部</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>オウコク ハクランカイ ホウコクショ ドウロブ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>[澳国博覧会事務局]</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1875.8序</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>600:3:4</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>道路部</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/46e4fe3f-3e7d-5f03-3639-d677f9b51cdb.json</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>46e4fe3f-3e7d-5f03-3639-d677f9b51cdb</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/46e4fe3f-3e7d-5f03-3639-d677f9b51cdb</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3dae14dc7e87a6f10acc786bf10c9a3c9694ac5a.jpg</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249167</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>048</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr"/>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/46e4fe3f-3e7d-5f03-3639-d677f9b51cdb/manifest</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
+      <c r="AH50" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>澳國博覽會報告書 山林部 上</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>オウコク ハクランカイ ホウコクショ サンリンブ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>[澳国博覧会事務局]</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1875.8序</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>600:3:5</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>山林部 上</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9bf458c7-9263-366c-360b-324933ab9469.json</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>9bf458c7-9263-366c-360b-324933ab9469</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/9bf458c7-9263-366c-360b-324933ab9469</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/275e954d62c2542b2c4c3d884dd686fc2ed45b4a.jpg</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249168</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>049</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9bf458c7-9263-366c-360b-324933ab9469/manifest</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>澳國博覽會報告書 山林部 中</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>オウコク ハクランカイ ホウコクショ サンリンブ</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>[澳国博覧会事務局]</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1875.8序</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>600:3:6</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>山林部 中</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4d89457e-1598-98c0-5511-332b13c81009.json</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>4d89457e-1598-98c0-5511-332b13c81009</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/4d89457e-1598-98c0-5511-332b13c81009</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f273b8ff4ff8e2479e4d46af8af27482154a2037.jpg</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249169</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>050</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4d89457e-1598-98c0-5511-332b13c81009/manifest</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
+      <c r="AH52" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>澳國博覽會報告書 [蚕業部 上-下]</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>オウコク ハクランカイ ホウコクショ サンギョウブ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>[澳国博覧会事務局]</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1875.8序</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>600:3:7</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>[蚕業部 上-下]</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/2b127bc1-7e6b-08d4-70a8-f16005ff7d88.json</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2b127bc1-7e6b-08d4-70a8-f16005ff7d88</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/2b127bc1-7e6b-08d4-70a8-f16005ff7d88</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/aa0576c478bfe2f1bd13a4b44e35dec80232c950.jpg</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249170</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>051</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/2b127bc1-7e6b-08d4-70a8-f16005ff7d88/manifest</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
+      <c r="AH53" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>澳國博覽會報告書 教育部 上</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>オウコク ハクランカイ ホウコクショ キョウイクブ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>[澳国博覧会事務局]</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1875.8序</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>600:3:8</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>教育部 上</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/bbccb4cf-954c-7ee2-3e2f-1ca03ceb8010.json</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>bbccb4cf-954c-7ee2-3e2f-1ca03ceb8010</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/bbccb4cf-954c-7ee2-3e2f-1ca03ceb8010</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/70860cf0b252ca2721b97a66ea6be903052436fa.jpg</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249171</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>052</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/bbccb4cf-954c-7ee2-3e2f-1ca03ceb8010/manifest</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="inlineStr"/>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
+      <c r="AH54" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>澳國博覽會報告書 教育部 下</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>オウコク ハクランカイ ホウコクショ キョウイクブ</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>[澳国博覧会事務局]</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1875.8序</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>600:3:9</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>教育部 下</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4cfd343e-3588-7466-543b-813a9c147fd0.json</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>4cfd343e-3588-7466-543b-813a9c147fd0</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/4cfd343e-3588-7466-543b-813a9c147fd0</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/eccac7d9fb486e1d22d87ae35c6ff6c7a8a8b1b7.jpg</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249172</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>053</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4cfd343e-3588-7466-543b-813a9c147fd0/manifest</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
+      <c r="AH55" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>澳國博覽會報告書 兵制部 上</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>オウコク ハクランカイ ホウコクショ ヘイセイブ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>[澳国博覧会事務局]</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1875.8序</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>600:3:10</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>兵制部 上</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1950682f-09ce-19f8-5793-dace838326ee.json</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1950682f-09ce-19f8-5793-dace838326ee</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/1950682f-09ce-19f8-5793-dace838326ee</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/9c6cd6ac5b3701ffc76a10d0c3c9bb16f05baf35.jpg</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249173</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>054</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1950682f-09ce-19f8-5793-dace838326ee/manifest</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
+      <c r="AH56" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>澳國博覽會報告書 [兵制部 中-下]</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>オウコク ハクランカイ ホウコクショ ヘイセイブ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>[澳国博覧会事務局]</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1875.8序</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>600:3:11</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>[兵制部 中-下]</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0ce52322-6da1-9a59-4711-982c02250b22.json</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>0ce52322-6da1-9a59-4711-982c02250b22</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/0ce52322-6da1-9a59-4711-982c02250b22</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2af66f92eb88a87bd94b72d307006b0eb99c4858.jpg</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249174</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>055</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0ce52322-6da1-9a59-4711-982c02250b22/manifest</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
+      <c r="AH57" t="n">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>澳國博覽會報告書 博覧会部 上</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>オウコク ハクランカイ ホウコクショ ハクランカイブ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>[澳国博覧会事務局]</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1875.8序</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>600:3:12</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>博覧会部 上</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a614068b-94a2-069e-6cc9-c9c27c2a37e7.json</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>a614068b-94a2-069e-6cc9-c9c27c2a37e7</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/a614068b-94a2-069e-6cc9-c9c27c2a37e7</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c3c242db43cdbe47d9ede3fab0bd0ba8d4bd3447.jpg</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249175</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>056</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a614068b-94a2-069e-6cc9-c9c27c2a37e7/manifest</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr"/>
+      <c r="AE58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr"/>
+      <c r="AH58" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>澳國博覽會報告書 銕路部</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>オウコク ハクランカイ ホウコクショ テツロブ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>[澳国博覧会事務局]</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1875.8序</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>600:3:13</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>銕路部</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/67adb7ee-13a9-8527-98dd-582ab6d1815e.json</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>67adb7ee-13a9-8527-98dd-582ab6d1815e</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/67adb7ee-13a9-8527-98dd-582ab6d1815e</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a5564ba6c799b80eaf9957eb0e2e966e4ee5a8bf.jpg</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249176</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>057</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr"/>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/67adb7ee-13a9-8527-98dd-582ab6d1815e/manifest</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr"/>
+      <c r="AE59" t="inlineStr"/>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr"/>
+      <c r="AH59" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>澳國博覽會報告書 [貿易部 上-下]</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>オウコク ハクランカイ ホウコクショ ボウエキブ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>[澳国博覧会事務局]</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1875.8序</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>600:3:14</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>[貿易部 上-下]</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/69cda5ec-59a8-75d3-9302-903deddd1b1b.json</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>69cda5ec-59a8-75d3-9302-903deddd1b1b</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/69cda5ec-59a8-75d3-9302-903deddd1b1b</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/5bbd2a3e2b4b04e446d48a8241dc2e1bf15460f3.jpg</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249177</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>058</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/69cda5ec-59a8-75d3-9302-903deddd1b1b/manifest</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr"/>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
+      <c r="AH60" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>澳國博覽會報告書 風俗制度部 上</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>オウコク ハクランカイ ホウコクショ フウゾク セイドブ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>[澳国博覧会事務局]</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1875.8序</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>600:3:15</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>風俗制度部 上</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4b5c431e-9ef6-3488-98b7-52829fe7a21f.json</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>4b5c431e-9ef6-3488-98b7-52829fe7a21f</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/4b5c431e-9ef6-3488-98b7-52829fe7a21f</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/94bb24db808b24eeb9166bb9d50279f6ccfe51f1.jpg</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249178</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>059</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4b5c431e-9ef6-3488-98b7-52829fe7a21f/manifest</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
+      <c r="AH61" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>澳國博覽會報告書 風俗制度部 下</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>オウコク ハクランカイ ホウコクショ フウゾク セイドブ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>[澳国博覧会事務局]</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>1875.8序</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>600:3:16</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>風俗制度部 下</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/84b46f92-0a4f-19b2-7e7e-3601f1cb0c75.json</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>84b46f92-0a4f-19b2-7e7e-3601f1cb0c75</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/84b46f92-0a4f-19b2-7e7e-3601f1cb0c75</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/975b0f324e47da401ca09a5d855a7cc0ed27315c.jpg</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249179</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>060</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/84b46f92-0a4f-19b2-7e7e-3601f1cb0c75/manifest</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
+      <c r="AH62" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>澳國博覽會報告書 附録 上</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>オウコク ハクランカイ ホウコクショ フロク</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>[澳国博覧会事務局]</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1875.8序</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>600:3:17</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>附録 上</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/738079d0-9eac-9d25-9169-d5de6bd2a600.json</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>738079d0-9eac-9d25-9169-d5de6bd2a600</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/738079d0-9eac-9d25-9169-d5de6bd2a600</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/18550641df2cb8c1a89b23c27b5e875eb945b3e8.jpg</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249180</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>061</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr"/>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/738079d0-9eac-9d25-9169-d5de6bd2a600/manifest</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr"/>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="inlineStr"/>
+      <c r="AH63" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>澳國博覽會報告書 附録 下</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>オウコク ハクランカイ ホウコクショ フロク</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>[澳国博覧会事務局]</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1875.8序</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>600:3:18</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>附録 下</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9f410855-9663-1ee3-a296-481ef7d57da6.json</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>9f410855-9663-1ee3-a296-481ef7d57da6</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/9f410855-9663-1ee3-a296-481ef7d57da6</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/62aa4fd87a6deb93694cb03b7e0b0f53629a05ce.jpg</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249181</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>062</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr"/>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9f410855-9663-1ee3-a296-481ef7d57da6/manifest</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr"/>
+      <c r="AE64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="inlineStr"/>
+      <c r="AH64" t="n">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/collections/agriculture/metadata/data.xlsx
+++ b/docs/collections/agriculture/metadata/data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH64"/>
+  <dimension ref="A1:AJ82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,100 +489,110 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>言語</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Series Alternative</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>iiif viewer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>ウェブサイトURL</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>アイテムURL</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>利用条件</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>サムネイル</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>機械可読ドキュメント</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>帰属</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>viewingDirection</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>viewingHint</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>コレクション</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>ソート用項目</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>西暦</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>IIIFマニフェストURI</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>IIIF Search API URI</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>アノテーション付きIIIFマニフェストURI</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Link to TAPAS Project</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Text with Rich Text Format</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t># of media</t>
         </is>
@@ -661,101 +671,111 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
+          <t>dcndl:materialType</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>dcterms:language</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>dcndl:seriesAlternative</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>iiif viewer</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>bibo:identifier</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>dcterms:isPartOf</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>dcterms:relation</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>dcterms:rights</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>foaf:thumbnail</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>rdfs:seeAlso</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>sc:attributionLabel</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>sc:viewingDirection</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>sc:viewingHint</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>uterms:databaseLabel</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>uterms:sort</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>uterms:year</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>uterms:manifestUri</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>uterms:searchApiUri</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>uterms:annotedManifest</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>uterms:linkToTapas</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>uterms:rtf</t>
         </is>
       </c>
-      <c r="AH2" t="n">
-        <v>6773</v>
+      <c r="AJ2" t="n">
+        <v>8545</v>
       </c>
     </row>
     <row r="3">
@@ -821,79 +841,81 @@
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d9115c2c-6c49-1f2b-515e-c67ea4332ab9.json</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>d9115c2c-6c49-1f2b-515e-c67ea4332ab9</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/d9115c2c-6c49-1f2b-515e-c67ea4332ab9</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a854fb44d17ab0f9f5bd95a2637c311ae0149a3a.jpg</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/275040</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the
 University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>001</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d9115c2c-6c49-1f2b-515e-c67ea4332ab9/manifest</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="n">
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="n">
         <v>13</v>
       </c>
     </row>
@@ -957,78 +979,80 @@
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6d032fb5-0a2f-6e04-9e3c-6bb5f604714f.json</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>6d032fb5-0a2f-6e04-9e3c-6bb5f604714f</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/6d032fb5-0a2f-6e04-9e3c-6bb5f604714f</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/ce5758680ca575da5f3a2c7c1a4efb30ec0575e9.jpg</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/275041</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>002</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6d032fb5-0a2f-6e04-9e3c-6bb5f604714f/manifest</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="n">
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="n">
         <v>29</v>
       </c>
     </row>
@@ -1091,78 +1115,80 @@
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/187cc82d-11e6-9912-9dd4-b4cca9b10970.json</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>187cc82d-11e6-9912-9dd4-b4cca9b10970</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/187cc82d-11e6-9912-9dd4-b4cca9b10970</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1ba32e3f0ffc84f504e4cc1d53c7cfe7bc88d7db.jpg</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/275042</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>003</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/187cc82d-11e6-9912-9dd4-b4cca9b10970/manifest</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="n">
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1209,74 +1235,76 @@
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/3e6f484d-a4e0-7073-4365-b287924d423a.json</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>3e6f484d-a4e0-7073-4365-b287924d423a</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/3e6f484d-a4e0-7073-4365-b287924d423a</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/dfb6622529735856cf83a97769bb6837c181d6ff.jpg</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/439369</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr">
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>004</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/3e6f484d-a4e0-7073-4365-b287924d423a/manifest</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="n">
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="n">
         <v>171</v>
       </c>
     </row>
@@ -1323,74 +1351,76 @@
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f3bfde97-6dfb-3f09-33af-0c615a250268.json</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>f3bfde97-6dfb-3f09-33af-0c615a250268</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/f3bfde97-6dfb-3f09-33af-0c615a250268</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/32e2196c46703505110c06bdbf92fa9ad8ca481c.jpg</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/439370</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr">
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>005</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f3bfde97-6dfb-3f09-33af-0c615a250268/manifest</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="n">
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="n">
         <v>173</v>
       </c>
     </row>
@@ -1437,74 +1467,76 @@
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a09fc5f4-8edc-0d46-7340-e2768dbf7a05.json</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>a09fc5f4-8edc-0d46-7340-e2768dbf7a05</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/a09fc5f4-8edc-0d46-7340-e2768dbf7a05</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/67749c791401a4d15b01ec7720cf21569b4c7c67.jpg</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/439371</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr">
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>006</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a09fc5f4-8edc-0d46-7340-e2768dbf7a05/manifest</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="n">
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="n">
         <v>178</v>
       </c>
     </row>
@@ -1551,74 +1583,76 @@
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9c79a3bb-34da-25bf-4243-4ba1709556a9.json</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>9c79a3bb-34da-25bf-4243-4ba1709556a9</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/9c79a3bb-34da-25bf-4243-4ba1709556a9</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a9c54d326cbc953cde434434eb26b6b81614129c.jpg</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/439372</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr">
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>007</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9c79a3bb-34da-25bf-4243-4ba1709556a9/manifest</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="n">
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="n">
         <v>142</v>
       </c>
     </row>
@@ -1665,74 +1699,76 @@
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/58f3ea6c-3626-9cbb-6cf8-33078f6e41bc.json</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>58f3ea6c-3626-9cbb-6cf8-33078f6e41bc</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/58f3ea6c-3626-9cbb-6cf8-33078f6e41bc</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/876c4079f5ebc054fab75c39ed25b18448581072.jpg</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/439373</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr">
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>008</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/58f3ea6c-3626-9cbb-6cf8-33078f6e41bc/manifest</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="n">
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="n">
         <v>145</v>
       </c>
     </row>
@@ -1784,69 +1820,71 @@
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b6e42779-162f-7bae-708c-bef438966890.json</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>b6e42779-162f-7bae-708c-bef438966890</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/b6e42779-162f-7bae-708c-bef438966890</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/14a8e8afeddd0ab3d4a4fd6cac5685bbab48346a.jpg</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/540593</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr">
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>009</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b6e42779-162f-7bae-708c-bef438966890/manifest</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="n">
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="n">
         <v>87</v>
       </c>
     </row>
@@ -1898,69 +1936,71 @@
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7a3e0c92-234b-1295-947b-d697d0d6955f.json</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>7a3e0c92-234b-1295-947b-d697d0d6955f</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/7a3e0c92-234b-1295-947b-d697d0d6955f</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/97c0529a040265b8bf2e67b949be578ed7e2d285.jpg</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/540592</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr">
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>010</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7a3e0c92-234b-1295-947b-d697d0d6955f/manifest</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="n">
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="n">
         <v>80</v>
       </c>
     </row>
@@ -2012,69 +2052,71 @@
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/df8094b2-597f-5dcf-6c06-28af31a74c49.json</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>df8094b2-597f-5dcf-6c06-28af31a74c49</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/df8094b2-597f-5dcf-6c06-28af31a74c49</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/90f647a0bb13d794aef2957aa6c46c235205639d.jpg</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/540591</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr">
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>011</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr">
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/df8094b2-597f-5dcf-6c06-28af31a74c49/manifest</t>
         </is>
       </c>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="n">
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="n">
         <v>162</v>
       </c>
     </row>
@@ -2126,69 +2168,71 @@
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/627f6b5d-4e4c-81e1-7954-bd451f567a45.json</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>627f6b5d-4e4c-81e1-7954-bd451f567a45</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/627f6b5d-4e4c-81e1-7954-bd451f567a45</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3dc15e9dbabbc0158d9913d72e3e11b9ecf4f6f6.jpg</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/540590</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr">
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>012</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr">
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/627f6b5d-4e4c-81e1-7954-bd451f567a45/manifest</t>
         </is>
       </c>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="n">
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="n">
         <v>29</v>
       </c>
     </row>
@@ -2240,69 +2284,71 @@
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b4814f58-5ae1-481d-0cfa-6938aa3a7620.json</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>b4814f58-5ae1-481d-0cfa-6938aa3a7620</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/b4814f58-5ae1-481d-0cfa-6938aa3a7620</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4fb75645c087af75f3055db0bb1e31fcfef680d6.jpg</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/540589</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr">
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>013</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr">
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b4814f58-5ae1-481d-0cfa-6938aa3a7620/manifest</t>
         </is>
       </c>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="n">
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="n">
         <v>50</v>
       </c>
     </row>
@@ -2354,69 +2400,71 @@
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/87c1c4a4-9cce-5b5f-a5a4-ad58e2240372.json</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>87c1c4a4-9cce-5b5f-a5a4-ad58e2240372</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/87c1c4a4-9cce-5b5f-a5a4-ad58e2240372</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1cbe04ccda9c3a0604f3331dc0aea9527c04b140.jpg</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/540588</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr">
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>014</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr">
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/87c1c4a4-9cce-5b5f-a5a4-ad58e2240372/manifest</t>
         </is>
       </c>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="n">
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="n">
         <v>85</v>
       </c>
     </row>
@@ -2468,69 +2516,71 @@
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/bb4b00b5-8a54-3698-656b-2b5baaa40938.json</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>bb4b00b5-8a54-3698-656b-2b5baaa40938</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/bb4b00b5-8a54-3698-656b-2b5baaa40938</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/5abde5eb843ebc906082579acb7b6b91347c34ad.jpg</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/540587</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr">
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>015</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr">
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/bb4b00b5-8a54-3698-656b-2b5baaa40938/manifest</t>
         </is>
       </c>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="n">
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="n">
         <v>78</v>
       </c>
     </row>
@@ -2582,69 +2632,71 @@
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/42dfe305-0e6e-4d22-298a-d3895726a29a.json</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>42dfe305-0e6e-4d22-298a-d3895726a29a</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/42dfe305-0e6e-4d22-298a-d3895726a29a</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3364e66d4f25b6291d583e1b29042f5f25fc98e1.jpg</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/540586</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="inlineStr">
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>016</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr">
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/42dfe305-0e6e-4d22-298a-d3895726a29a/manifest</t>
         </is>
       </c>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="n">
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="n">
         <v>71</v>
       </c>
     </row>
@@ -2696,69 +2748,71 @@
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/6041ed83-59e7-7bc0-196d-c7ed8d01673d.json</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>6041ed83-59e7-7bc0-196d-c7ed8d01673d</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/6041ed83-59e7-7bc0-196d-c7ed8d01673d</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0fd408ca8f01b4b48b70c80355fcf0e8b4f63d97.jpg</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/540585</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="inlineStr">
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>017</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr">
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/6041ed83-59e7-7bc0-196d-c7ed8d01673d/manifest</t>
         </is>
       </c>
-      <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="n">
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="n">
         <v>59</v>
       </c>
     </row>
@@ -2810,69 +2864,71 @@
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/5bfde8bf-0b54-7848-97d6-1ee30cf9a645.json</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>5bfde8bf-0b54-7848-97d6-1ee30cf9a645</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/5bfde8bf-0b54-7848-97d6-1ee30cf9a645</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/bf05396c6209233d94c7883e25d8a4cf3624d93e.jpg</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/540584</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
-      <c r="Y20" t="inlineStr"/>
-      <c r="Z20" t="inlineStr">
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>018</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr">
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/5bfde8bf-0b54-7848-97d6-1ee30cf9a645/manifest</t>
         </is>
       </c>
-      <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="n">
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="n">
         <v>47</v>
       </c>
     </row>
@@ -2924,69 +2980,71 @@
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7844f0c7-2434-7b74-15df-c74b0e3c8e38.json</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>7844f0c7-2434-7b74-15df-c74b0e3c8e38</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/7844f0c7-2434-7b74-15df-c74b0e3c8e38</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/64363d5cbfe12a51092e585f5f6f940ad29ec7e6.jpg</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/540583</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="inlineStr">
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>019</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr">
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7844f0c7-2434-7b74-15df-c74b0e3c8e38/manifest</t>
         </is>
       </c>
-      <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="n">
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="n">
         <v>46</v>
       </c>
     </row>
@@ -3038,69 +3096,71 @@
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/29d63e58-754f-7565-a41a-29cc2d5e4e3e.json</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>29d63e58-754f-7565-a41a-29cc2d5e4e3e</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/29d63e58-754f-7565-a41a-29cc2d5e4e3e</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/28276688ee682e8065bd9bec5c8e77ad77cc8f53.jpg</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/540582</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr">
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>020</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr">
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/29d63e58-754f-7565-a41a-29cc2d5e4e3e/manifest</t>
         </is>
       </c>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="n">
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="n">
         <v>49</v>
       </c>
     </row>
@@ -3156,69 +3216,71 @@
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c2466a42-0add-7f2b-7d11-58aaebea953f.json</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>c2466a42-0add-7f2b-7d11-58aaebea953f</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/c2466a42-0add-7f2b-7d11-58aaebea953f</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="W23" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/101b027d6bc01f45b781ec4b1b5ade9e683fc0e2.jpg</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541553</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
-      <c r="Y23" t="inlineStr"/>
-      <c r="Z23" t="inlineStr">
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>021</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr">
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c2466a42-0add-7f2b-7d11-58aaebea953f/manifest</t>
         </is>
       </c>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="n">
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="n">
         <v>22</v>
       </c>
     </row>
@@ -3274,69 +3336,71 @@
         </is>
       </c>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/2c310bb0-6cb1-4f7b-2b7d-7d6255cf680e.json</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>2c310bb0-6cb1-4f7b-2b7d-7d6255cf680e</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/2c310bb0-6cb1-4f7b-2b7d-7d6255cf680e</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="W24" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/83a4e1b5b89b77ef327aaabfe7ae54efcc673b83.jpg</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541552</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
-      <c r="Y24" t="inlineStr"/>
-      <c r="Z24" t="inlineStr">
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>022</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr">
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/2c310bb0-6cb1-4f7b-2b7d-7d6255cf680e/manifest</t>
         </is>
       </c>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="n">
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="n">
         <v>102</v>
       </c>
     </row>
@@ -3392,69 +3456,71 @@
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/70f02bc2-6f66-84ec-3578-058a8d03668c.json</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>70f02bc2-6f66-84ec-3578-058a8d03668c</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/70f02bc2-6f66-84ec-3578-058a8d03668c</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="W25" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f647534e44867cf617598f2d51e26d05643d0948.jpg</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541551</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
-      <c r="Y25" t="inlineStr"/>
-      <c r="Z25" t="inlineStr">
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>023</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr">
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/70f02bc2-6f66-84ec-3578-058a8d03668c/manifest</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="n">
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="n">
         <v>84</v>
       </c>
     </row>
@@ -3514,69 +3580,71 @@
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f9dbea50-3d74-5d6e-03f2-b5bf339b5a2b.json</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>f9dbea50-3d74-5d6e-03f2-b5bf339b5a2b</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/f9dbea50-3d74-5d6e-03f2-b5bf339b5a2b</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="W26" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/674d9cadf351cbd2facc9305e02d0769cbb9aa97.jpg</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541550</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
-      <c r="Y26" t="inlineStr"/>
-      <c r="Z26" t="inlineStr">
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>024</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr"/>
-      <c r="AC26" t="inlineStr">
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f9dbea50-3d74-5d6e-03f2-b5bf339b5a2b/manifest</t>
         </is>
       </c>
-      <c r="AD26" t="inlineStr"/>
-      <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="n">
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="n">
         <v>90</v>
       </c>
     </row>
@@ -3632,69 +3700,71 @@
         </is>
       </c>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a2af6812-7fd8-2cf2-759d-11fff8990e95.json</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>a2af6812-7fd8-2cf2-759d-11fff8990e95</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/a2af6812-7fd8-2cf2-759d-11fff8990e95</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="W27" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/79eddc772afeb6a83b0f3c57230c89b50848b7c2.jpg</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541549</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
-      <c r="Y27" t="inlineStr"/>
-      <c r="Z27" t="inlineStr">
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>025</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr">
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a2af6812-7fd8-2cf2-759d-11fff8990e95/manifest</t>
         </is>
       </c>
-      <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
-      <c r="AH27" t="n">
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="n">
         <v>22</v>
       </c>
     </row>
@@ -3750,69 +3820,71 @@
         </is>
       </c>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/2da73342-76a3-0edc-8b07-d866f06d5ea3.json</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>2da73342-76a3-0edc-8b07-d866f06d5ea3</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/2da73342-76a3-0edc-8b07-d866f06d5ea3</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="W28" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a25f6e6a6f3dc7075cf046171131e1dd30da1906.jpg</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541548</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
-      <c r="Y28" t="inlineStr"/>
-      <c r="Z28" t="inlineStr">
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>026</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="inlineStr">
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/2da73342-76a3-0edc-8b07-d866f06d5ea3/manifest</t>
         </is>
       </c>
-      <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="n">
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="n">
         <v>21</v>
       </c>
     </row>
@@ -3868,69 +3940,71 @@
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/e443b3ea-830a-907d-42a9-cb4036f27a96.json</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>e443b3ea-830a-907d-42a9-cb4036f27a96</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/e443b3ea-830a-907d-42a9-cb4036f27a96</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="W29" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/6f34c6d2435321d152f7259e81741f4a89f6546b.jpg</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541547</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
-      <c r="Y29" t="inlineStr"/>
-      <c r="Z29" t="inlineStr">
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>027</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr">
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/e443b3ea-830a-907d-42a9-cb4036f27a96/manifest</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="n">
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="n">
         <v>20</v>
       </c>
     </row>
@@ -3986,69 +4060,71 @@
         </is>
       </c>
       <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/8d83cc45-79ff-0188-659b-7ca5fd48849e.json</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>8d83cc45-79ff-0188-659b-7ca5fd48849e</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/8d83cc45-79ff-0188-659b-7ca5fd48849e</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="W30" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/408216c089708be5af32f74482148d3a4efdd097.jpg</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541546</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
-      <c r="Y30" t="inlineStr"/>
-      <c r="Z30" t="inlineStr">
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>028</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr">
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/8d83cc45-79ff-0188-659b-7ca5fd48849e/manifest</t>
         </is>
       </c>
-      <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
-      <c r="AH30" t="n">
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="n">
         <v>24</v>
       </c>
     </row>
@@ -4104,69 +4180,71 @@
         </is>
       </c>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/30c60644-40b8-a0d3-9231-3b6320c7843e.json</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>30c60644-40b8-a0d3-9231-3b6320c7843e</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/30c60644-40b8-a0d3-9231-3b6320c7843e</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="W31" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/03a77a3b6451aa20e1423800ecae92ce21c42553.jpg</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541545</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr">
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>029</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="inlineStr">
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/30c60644-40b8-a0d3-9231-3b6320c7843e/manifest</t>
         </is>
       </c>
-      <c r="AD31" t="inlineStr"/>
-      <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
-      <c r="AH31" t="n">
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="n">
         <v>22</v>
       </c>
     </row>
@@ -4222,69 +4300,71 @@
         </is>
       </c>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/05fc859e-3db1-5c8b-323f-e11d3e9010cc.json</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>05fc859e-3db1-5c8b-323f-e11d3e9010cc</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/05fc859e-3db1-5c8b-323f-e11d3e9010cc</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="W32" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b9e94c996c3c17fd669ef4fa8dffb81e33e9ac1b.jpg</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541544</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr">
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>030</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr"/>
-      <c r="AC32" t="inlineStr">
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/05fc859e-3db1-5c8b-323f-e11d3e9010cc/manifest</t>
         </is>
       </c>
-      <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
-      <c r="AH32" t="n">
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="n">
         <v>20</v>
       </c>
     </row>
@@ -4340,69 +4420,71 @@
         </is>
       </c>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0717b584-7f27-70c4-70e9-0dfc7ed28f77.json</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>0717b584-7f27-70c4-70e9-0dfc7ed28f77</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/0717b584-7f27-70c4-70e9-0dfc7ed28f77</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="W33" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/6baf5a7867abd52890ddf2c0e298dde3871036fa.jpg</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541543</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
-      <c r="Y33" t="inlineStr"/>
-      <c r="Z33" t="inlineStr">
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>031</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr"/>
-      <c r="AC33" t="inlineStr">
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0717b584-7f27-70c4-70e9-0dfc7ed28f77/manifest</t>
         </is>
       </c>
-      <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="n">
+      <c r="AH33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr"/>
+      <c r="AJ33" t="n">
         <v>20</v>
       </c>
     </row>
@@ -4458,69 +4540,71 @@
         </is>
       </c>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4e17a945-4320-171d-142e-bd3838ba1cfa.json</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>4e17a945-4320-171d-142e-bd3838ba1cfa</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/4e17a945-4320-171d-142e-bd3838ba1cfa</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="W34" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1534e0eaa9a76cbddc00ac2cf517eacce5f4bc43.jpg</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541542</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
-      <c r="Y34" t="inlineStr"/>
-      <c r="Z34" t="inlineStr">
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>032</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr"/>
-      <c r="AC34" t="inlineStr">
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4e17a945-4320-171d-142e-bd3838ba1cfa/manifest</t>
         </is>
       </c>
-      <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="n">
+      <c r="AH34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr"/>
+      <c r="AJ34" t="n">
         <v>21</v>
       </c>
     </row>
@@ -4580,69 +4664,71 @@
         </is>
       </c>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/97a6ecb3-5cb2-08c3-0d4f-e057b8f2258b.json</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>97a6ecb3-5cb2-08c3-0d4f-e057b8f2258b</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/97a6ecb3-5cb2-08c3-0d4f-e057b8f2258b</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4338a576fa00a1b57f1dbf414ffeaed14fad4498.jpg</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541541</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
-      <c r="Y35" t="inlineStr"/>
-      <c r="Z35" t="inlineStr">
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA35" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>033</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr"/>
-      <c r="AC35" t="inlineStr">
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/97a6ecb3-5cb2-08c3-0d4f-e057b8f2258b/manifest</t>
         </is>
       </c>
-      <c r="AD35" t="inlineStr"/>
-      <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="inlineStr"/>
-      <c r="AH35" t="n">
+      <c r="AH35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr"/>
+      <c r="AJ35" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4698,69 +4784,71 @@
         </is>
       </c>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/c9f1ab4e-6bf9-997c-95a7-572c5e6b2597.json</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>c9f1ab4e-6bf9-997c-95a7-572c5e6b2597</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/c9f1ab4e-6bf9-997c-95a7-572c5e6b2597</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="W36" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2c13ea887a4ea6f06c7e832e01a70527eeeb6617.jpg</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/541540</t>
         </is>
       </c>
-      <c r="W36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
-      <c r="Y36" t="inlineStr"/>
-      <c r="Z36" t="inlineStr">
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA36" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>034</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr"/>
-      <c r="AC36" t="inlineStr">
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/c9f1ab4e-6bf9-997c-95a7-572c5e6b2597/manifest</t>
         </is>
       </c>
-      <c r="AD36" t="inlineStr"/>
-      <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="inlineStr"/>
-      <c r="AH36" t="n">
+      <c r="AH36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr"/>
+      <c r="AJ36" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4808,69 +4896,71 @@
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4e0dc54b-2d8a-7d80-2f37-40842b0ea589.json</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>4e0dc54b-2d8a-7d80-2f37-40842b0ea589</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/4e0dc54b-2d8a-7d80-2f37-40842b0ea589</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="W37" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f654ef92709303ef6714617681b0d136403c1537.jpg</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249154</t>
         </is>
       </c>
-      <c r="W37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="inlineStr"/>
-      <c r="Z37" t="inlineStr">
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA37" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>035</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr"/>
-      <c r="AC37" t="inlineStr">
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4e0dc54b-2d8a-7d80-2f37-40842b0ea589/manifest</t>
         </is>
       </c>
-      <c r="AD37" t="inlineStr"/>
-      <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="inlineStr"/>
-      <c r="AH37" t="n">
+      <c r="AH37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr"/>
+      <c r="AJ37" t="n">
         <v>547</v>
       </c>
     </row>
@@ -4918,69 +5008,71 @@
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/29e4da03-7e96-4dd2-68ba-f23004321f33.json</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>29e4da03-7e96-4dd2-68ba-f23004321f33</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr">
+      <c r="U38" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/29e4da03-7e96-4dd2-68ba-f23004321f33</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
+      <c r="V38" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="W38" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/39b8badc7512534a6518ccfd07746632d4bb85c1.jpg</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249156</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="Y38" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
-      <c r="Y38" t="inlineStr"/>
-      <c r="Z38" t="inlineStr">
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA38" t="inlineStr">
+      <c r="AC38" t="inlineStr">
         <is>
           <t>036</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr"/>
-      <c r="AC38" t="inlineStr">
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/29e4da03-7e96-4dd2-68ba-f23004321f33/manifest</t>
         </is>
       </c>
-      <c r="AD38" t="inlineStr"/>
-      <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="inlineStr"/>
-      <c r="AH38" t="n">
+      <c r="AH38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr"/>
+      <c r="AJ38" t="n">
         <v>371</v>
       </c>
     </row>
@@ -5028,69 +5120,71 @@
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f26d3e18-58ef-0ce5-8f74-ca48dfc99da0.json</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>f26d3e18-58ef-0ce5-8f74-ca48dfc99da0</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr">
+      <c r="U39" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/f26d3e18-58ef-0ce5-8f74-ca48dfc99da0</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
+      <c r="V39" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e9ef6f044676a534bb275bb8a09074bdd79b06e6.jpg</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249157</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
+      <c r="Y39" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="inlineStr"/>
-      <c r="Z39" t="inlineStr">
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA39" t="inlineStr">
+      <c r="AC39" t="inlineStr">
         <is>
           <t>037</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr"/>
-      <c r="AC39" t="inlineStr">
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f26d3e18-58ef-0ce5-8f74-ca48dfc99da0/manifest</t>
         </is>
       </c>
-      <c r="AD39" t="inlineStr"/>
-      <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="inlineStr"/>
-      <c r="AH39" t="n">
+      <c r="AH39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr"/>
+      <c r="AJ39" t="n">
         <v>632</v>
       </c>
     </row>
@@ -5138,69 +5232,71 @@
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/5a5250d3-95aa-066a-3a2e-1922bc793618.json</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>5a5250d3-95aa-066a-3a2e-1922bc793618</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr">
+      <c r="U40" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/5a5250d3-95aa-066a-3a2e-1922bc793618</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="V40" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="W40" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/717ac355eec81f9adc4953d48a8d23e9bfe11d1b.jpg</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249155</t>
         </is>
       </c>
-      <c r="W40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
-      <c r="Y40" t="inlineStr"/>
-      <c r="Z40" t="inlineStr">
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA40" t="inlineStr">
+      <c r="AC40" t="inlineStr">
         <is>
           <t>038</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr"/>
-      <c r="AC40" t="inlineStr">
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/5a5250d3-95aa-066a-3a2e-1922bc793618/manifest</t>
         </is>
       </c>
-      <c r="AD40" t="inlineStr"/>
-      <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="inlineStr"/>
-      <c r="AH40" t="n">
+      <c r="AH40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr"/>
+      <c r="AJ40" t="n">
         <v>679</v>
       </c>
     </row>
@@ -5252,69 +5348,71 @@
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d6210358-1b3e-2274-688f-08add7189baf.json</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>d6210358-1b3e-2274-688f-08add7189baf</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/d6210358-1b3e-2274-688f-08add7189baf</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="W41" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4b7300af4b7d19dee9e9568a7b67af3098480e23.jpg</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249158</t>
         </is>
       </c>
-      <c r="W41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
-      <c r="Y41" t="inlineStr"/>
-      <c r="Z41" t="inlineStr">
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AC41" t="inlineStr">
         <is>
           <t>039</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr"/>
-      <c r="AC41" t="inlineStr">
+      <c r="AD41" t="inlineStr"/>
+      <c r="AE41" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d6210358-1b3e-2274-688f-08add7189baf/manifest</t>
         </is>
       </c>
-      <c r="AD41" t="inlineStr"/>
-      <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="inlineStr"/>
-      <c r="AH41" t="n">
+      <c r="AH41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr"/>
+      <c r="AJ41" t="n">
         <v>368</v>
       </c>
     </row>
@@ -5366,69 +5464,71 @@
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4d74f571-9b2d-675f-0683-8a193cfe5e54.json</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>4d74f571-9b2d-675f-0683-8a193cfe5e54</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/4d74f571-9b2d-675f-0683-8a193cfe5e54</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="W42" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3c1ae77ce4997a14770e524fa8d1cc6fd4245301.jpg</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249159</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
-      <c r="Y42" t="inlineStr"/>
-      <c r="Z42" t="inlineStr">
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AC42" t="inlineStr">
         <is>
           <t>040</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr"/>
-      <c r="AC42" t="inlineStr">
+      <c r="AD42" t="inlineStr"/>
+      <c r="AE42" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4d74f571-9b2d-675f-0683-8a193cfe5e54/manifest</t>
         </is>
       </c>
-      <c r="AD42" t="inlineStr"/>
-      <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="inlineStr"/>
-      <c r="AH42" t="n">
+      <c r="AH42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr"/>
+      <c r="AJ42" t="n">
         <v>110</v>
       </c>
     </row>
@@ -5480,69 +5580,71 @@
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/44f9950d-5b3e-9234-19b6-c7b43c4509a0.json</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>44f9950d-5b3e-9234-19b6-c7b43c4509a0</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/44f9950d-5b3e-9234-19b6-c7b43c4509a0</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="W43" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/07197f0c25e6af616ea5dedd6ac9a24fbf431adf.jpg</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249160</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="Y43" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
-      <c r="Y43" t="inlineStr"/>
-      <c r="Z43" t="inlineStr">
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr">
+      <c r="AC43" t="inlineStr">
         <is>
           <t>041</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr"/>
-      <c r="AC43" t="inlineStr">
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/44f9950d-5b3e-9234-19b6-c7b43c4509a0/manifest</t>
         </is>
       </c>
-      <c r="AD43" t="inlineStr"/>
-      <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="inlineStr"/>
-      <c r="AH43" t="n">
+      <c r="AH43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr"/>
+      <c r="AJ43" t="n">
         <v>68</v>
       </c>
     </row>
@@ -5602,73 +5704,75 @@
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/7641f4d6-2186-27cb-a14b-5557175d5cff.json</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>7641f4d6-2186-27cb-a14b-5557175d5cff</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/7641f4d6-2186-27cb-a14b-5557175d5cff</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="W44" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/d2092dcb435163ecdbb4dd8a6dd9378acfb820b6.jpg</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249161</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="Y44" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="Z44" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="Y44" t="inlineStr"/>
-      <c r="Z44" t="inlineStr">
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr">
+      <c r="AC44" t="inlineStr">
         <is>
           <t>042</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr"/>
-      <c r="AC44" t="inlineStr">
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/7641f4d6-2186-27cb-a14b-5557175d5cff/manifest</t>
         </is>
       </c>
-      <c r="AD44" t="inlineStr"/>
-      <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="inlineStr"/>
-      <c r="AH44" t="n">
+      <c r="AH44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr"/>
+      <c r="AJ44" t="n">
         <v>23</v>
       </c>
     </row>
@@ -5728,73 +5832,75 @@
         </is>
       </c>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/d46eb2e4-3308-8768-3c2c-c835345d4f16.json</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>d46eb2e4-3308-8768-3c2c-c835345d4f16</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/d46eb2e4-3308-8768-3c2c-c835345d4f16</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1e71e9250db867c3aa06c22c0c59903d16891138.jpg</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249162</t>
         </is>
       </c>
-      <c r="W45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="Z45" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="Y45" t="inlineStr"/>
-      <c r="Z45" t="inlineStr">
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AC45" t="inlineStr">
         <is>
           <t>043</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr"/>
-      <c r="AC45" t="inlineStr">
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/d46eb2e4-3308-8768-3c2c-c835345d4f16/manifest</t>
         </is>
       </c>
-      <c r="AD45" t="inlineStr"/>
-      <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="inlineStr"/>
-      <c r="AH45" t="n">
+      <c r="AH45" t="inlineStr"/>
+      <c r="AI45" t="inlineStr"/>
+      <c r="AJ45" t="n">
         <v>32</v>
       </c>
     </row>
@@ -5854,73 +5960,75 @@
         </is>
       </c>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/afc99ebe-2ecc-8868-360c-d0de65d61e98.json</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>afc99ebe-2ecc-8868-360c-d0de65d61e98</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/afc99ebe-2ecc-8868-360c-d0de65d61e98</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="W46" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0fbc84dd2e140498a4cc78d031034a5d2412263b.jpg</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249163</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="Y46" t="inlineStr"/>
-      <c r="Z46" t="inlineStr">
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA46" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>044</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr"/>
-      <c r="AC46" t="inlineStr">
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/afc99ebe-2ecc-8868-360c-d0de65d61e98/manifest</t>
         </is>
       </c>
-      <c r="AD46" t="inlineStr"/>
-      <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="inlineStr"/>
-      <c r="AH46" t="n">
+      <c r="AH46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr"/>
+      <c r="AJ46" t="n">
         <v>55</v>
       </c>
     </row>
@@ -5976,73 +6084,75 @@
         </is>
       </c>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1562ca02-6f67-313f-4f4e-14214acc7f40.json</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>1562ca02-6f67-313f-4f4e-14214acc7f40</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/1562ca02-6f67-313f-4f4e-14214acc7f40</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="W47" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/450226c5ec3d99e7a1cc07fc89c7752e8e67be35.jpg</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249164</t>
         </is>
       </c>
-      <c r="W47" t="inlineStr">
+      <c r="Y47" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
+      <c r="Z47" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="Y47" t="inlineStr"/>
-      <c r="Z47" t="inlineStr">
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA47" t="inlineStr">
+      <c r="AC47" t="inlineStr">
         <is>
           <t>045</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr"/>
-      <c r="AC47" t="inlineStr">
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1562ca02-6f67-313f-4f4e-14214acc7f40/manifest</t>
         </is>
       </c>
-      <c r="AD47" t="inlineStr"/>
-      <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="inlineStr"/>
-      <c r="AH47" t="n">
+      <c r="AH47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr"/>
+      <c r="AJ47" t="n">
         <v>120</v>
       </c>
     </row>
@@ -6098,73 +6208,75 @@
         </is>
       </c>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/00d56783-91e9-80a4-35b8-33f959a45063.json</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>00d56783-91e9-80a4-35b8-33f959a45063</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/00d56783-91e9-80a4-35b8-33f959a45063</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="W48" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/6e5d14a047d82c524e04281e4a622f03f8f8f9d6.jpg</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249165</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr">
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA48" t="inlineStr">
+      <c r="AC48" t="inlineStr">
         <is>
           <t>046</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr"/>
-      <c r="AC48" t="inlineStr">
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/00d56783-91e9-80a4-35b8-33f959a45063/manifest</t>
         </is>
       </c>
-      <c r="AD48" t="inlineStr"/>
-      <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="inlineStr"/>
-      <c r="AH48" t="n">
+      <c r="AH48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr"/>
+      <c r="AJ48" t="n">
         <v>76</v>
       </c>
     </row>
@@ -6220,73 +6332,75 @@
         </is>
       </c>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/19dd4309-44fb-3da3-6648-2b8057719ca1.json</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>19dd4309-44fb-3da3-6648-2b8057719ca1</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/19dd4309-44fb-3da3-6648-2b8057719ca1</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="W49" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/8e36e9cf933bce99e082ba384f4bc84c7fd702cd.jpg</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249166</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="Y49" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr">
+      <c r="AA49" t="inlineStr"/>
+      <c r="AB49" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA49" t="inlineStr">
+      <c r="AC49" t="inlineStr">
         <is>
           <t>047</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr"/>
-      <c r="AC49" t="inlineStr">
+      <c r="AD49" t="inlineStr"/>
+      <c r="AE49" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/19dd4309-44fb-3da3-6648-2b8057719ca1/manifest</t>
         </is>
       </c>
-      <c r="AD49" t="inlineStr"/>
-      <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="inlineStr"/>
-      <c r="AH49" t="n">
+      <c r="AH49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr"/>
+      <c r="AJ49" t="n">
         <v>61</v>
       </c>
     </row>
@@ -6342,73 +6456,75 @@
         </is>
       </c>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/46e4fe3f-3e7d-5f03-3639-d677f9b51cdb.json</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>46e4fe3f-3e7d-5f03-3639-d677f9b51cdb</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/46e4fe3f-3e7d-5f03-3639-d677f9b51cdb</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="W50" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/3dae14dc7e87a6f10acc786bf10c9a3c9694ac5a.jpg</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249167</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="Z50" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr">
+      <c r="AA50" t="inlineStr"/>
+      <c r="AB50" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA50" t="inlineStr">
+      <c r="AC50" t="inlineStr">
         <is>
           <t>048</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr"/>
-      <c r="AC50" t="inlineStr">
+      <c r="AD50" t="inlineStr"/>
+      <c r="AE50" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/46e4fe3f-3e7d-5f03-3639-d677f9b51cdb/manifest</t>
         </is>
       </c>
-      <c r="AD50" t="inlineStr"/>
-      <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="inlineStr"/>
-      <c r="AH50" t="n">
+      <c r="AH50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr"/>
+      <c r="AJ50" t="n">
         <v>102</v>
       </c>
     </row>
@@ -6464,73 +6580,75 @@
         </is>
       </c>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9bf458c7-9263-366c-360b-324933ab9469.json</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>9bf458c7-9263-366c-360b-324933ab9469</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/9bf458c7-9263-366c-360b-324933ab9469</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="W51" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/275e954d62c2542b2c4c3d884dd686fc2ed45b4a.jpg</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249168</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="Y51" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr">
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA51" t="inlineStr">
+      <c r="AC51" t="inlineStr">
         <is>
           <t>049</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr"/>
-      <c r="AC51" t="inlineStr">
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9bf458c7-9263-366c-360b-324933ab9469/manifest</t>
         </is>
       </c>
-      <c r="AD51" t="inlineStr"/>
-      <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="inlineStr"/>
-      <c r="AH51" t="n">
+      <c r="AH51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr"/>
+      <c r="AJ51" t="n">
         <v>51</v>
       </c>
     </row>
@@ -6586,73 +6704,75 @@
         </is>
       </c>
       <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4d89457e-1598-98c0-5511-332b13c81009.json</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>4d89457e-1598-98c0-5511-332b13c81009</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/4d89457e-1598-98c0-5511-332b13c81009</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="W52" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f273b8ff4ff8e2479e4d46af8af27482154a2037.jpg</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249169</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="Y52" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr">
+      <c r="AA52" t="inlineStr"/>
+      <c r="AB52" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA52" t="inlineStr">
+      <c r="AC52" t="inlineStr">
         <is>
           <t>050</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr"/>
-      <c r="AC52" t="inlineStr">
+      <c r="AD52" t="inlineStr"/>
+      <c r="AE52" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4d89457e-1598-98c0-5511-332b13c81009/manifest</t>
         </is>
       </c>
-      <c r="AD52" t="inlineStr"/>
-      <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="inlineStr"/>
-      <c r="AH52" t="n">
+      <c r="AH52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr"/>
+      <c r="AJ52" t="n">
         <v>68</v>
       </c>
     </row>
@@ -6708,73 +6828,75 @@
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/2b127bc1-7e6b-08d4-70a8-f16005ff7d88.json</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>2b127bc1-7e6b-08d4-70a8-f16005ff7d88</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/2b127bc1-7e6b-08d4-70a8-f16005ff7d88</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="V53" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="W53" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/aa0576c478bfe2f1bd13a4b44e35dec80232c950.jpg</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249170</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr">
+      <c r="AA53" t="inlineStr"/>
+      <c r="AB53" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA53" t="inlineStr">
+      <c r="AC53" t="inlineStr">
         <is>
           <t>051</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr"/>
-      <c r="AC53" t="inlineStr">
+      <c r="AD53" t="inlineStr"/>
+      <c r="AE53" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/2b127bc1-7e6b-08d4-70a8-f16005ff7d88/manifest</t>
         </is>
       </c>
-      <c r="AD53" t="inlineStr"/>
-      <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="inlineStr"/>
-      <c r="AH53" t="n">
+      <c r="AH53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr"/>
+      <c r="AJ53" t="n">
         <v>167</v>
       </c>
     </row>
@@ -6830,73 +6952,75 @@
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/bbccb4cf-954c-7ee2-3e2f-1ca03ceb8010.json</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>bbccb4cf-954c-7ee2-3e2f-1ca03ceb8010</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/bbccb4cf-954c-7ee2-3e2f-1ca03ceb8010</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="V54" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="W54" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/70860cf0b252ca2721b97a66ea6be903052436fa.jpg</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249171</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr">
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA54" t="inlineStr">
+      <c r="AC54" t="inlineStr">
         <is>
           <t>052</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr"/>
-      <c r="AC54" t="inlineStr">
+      <c r="AD54" t="inlineStr"/>
+      <c r="AE54" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/bbccb4cf-954c-7ee2-3e2f-1ca03ceb8010/manifest</t>
         </is>
       </c>
-      <c r="AD54" t="inlineStr"/>
-      <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="inlineStr"/>
-      <c r="AH54" t="n">
+      <c r="AH54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr"/>
+      <c r="AJ54" t="n">
         <v>108</v>
       </c>
     </row>
@@ -6952,73 +7076,75 @@
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4cfd343e-3588-7466-543b-813a9c147fd0.json</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>4cfd343e-3588-7466-543b-813a9c147fd0</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/4cfd343e-3588-7466-543b-813a9c147fd0</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="V55" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="W55" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/eccac7d9fb486e1d22d87ae35c6ff6c7a8a8b1b7.jpg</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249172</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
+      <c r="Y55" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
+      <c r="Z55" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr">
+      <c r="AA55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA55" t="inlineStr">
+      <c r="AC55" t="inlineStr">
         <is>
           <t>053</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr"/>
-      <c r="AC55" t="inlineStr">
+      <c r="AD55" t="inlineStr"/>
+      <c r="AE55" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4cfd343e-3588-7466-543b-813a9c147fd0/manifest</t>
         </is>
       </c>
-      <c r="AD55" t="inlineStr"/>
-      <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="inlineStr"/>
-      <c r="AH55" t="n">
+      <c r="AH55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr"/>
+      <c r="AJ55" t="n">
         <v>76</v>
       </c>
     </row>
@@ -7074,73 +7200,75 @@
         </is>
       </c>
       <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1950682f-09ce-19f8-5793-dace838326ee.json</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>1950682f-09ce-19f8-5793-dace838326ee</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/1950682f-09ce-19f8-5793-dace838326ee</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="V56" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="W56" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/9c6cd6ac5b3701ffc76a10d0c3c9bb16f05baf35.jpg</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249173</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr">
+      <c r="Y56" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr">
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA56" t="inlineStr">
+      <c r="AC56" t="inlineStr">
         <is>
           <t>054</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr"/>
-      <c r="AC56" t="inlineStr">
+      <c r="AD56" t="inlineStr"/>
+      <c r="AE56" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1950682f-09ce-19f8-5793-dace838326ee/manifest</t>
         </is>
       </c>
-      <c r="AD56" t="inlineStr"/>
-      <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="inlineStr"/>
-      <c r="AH56" t="n">
+      <c r="AH56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr"/>
+      <c r="AJ56" t="n">
         <v>61</v>
       </c>
     </row>
@@ -7196,73 +7324,75 @@
         </is>
       </c>
       <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/0ce52322-6da1-9a59-4711-982c02250b22.json</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>0ce52322-6da1-9a59-4711-982c02250b22</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/0ce52322-6da1-9a59-4711-982c02250b22</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="V57" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="W57" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/2af66f92eb88a87bd94b72d307006b0eb99c4858.jpg</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249174</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
+      <c r="Y57" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
+      <c r="Z57" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr">
+      <c r="AA57" t="inlineStr"/>
+      <c r="AB57" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA57" t="inlineStr">
+      <c r="AC57" t="inlineStr">
         <is>
           <t>055</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr"/>
-      <c r="AC57" t="inlineStr">
+      <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/0ce52322-6da1-9a59-4711-982c02250b22/manifest</t>
         </is>
       </c>
-      <c r="AD57" t="inlineStr"/>
-      <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="inlineStr"/>
-      <c r="AH57" t="n">
+      <c r="AH57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr"/>
+      <c r="AJ57" t="n">
         <v>142</v>
       </c>
     </row>
@@ -7318,73 +7448,75 @@
         </is>
       </c>
       <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/a614068b-94a2-069e-6cc9-c9c27c2a37e7.json</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>a614068b-94a2-069e-6cc9-c9c27c2a37e7</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/a614068b-94a2-069e-6cc9-c9c27c2a37e7</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="V58" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="W58" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/c3c242db43cdbe47d9ede3fab0bd0ba8d4bd3447.jpg</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249175</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
+      <c r="Y58" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
+      <c r="Z58" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr">
+      <c r="AA58" t="inlineStr"/>
+      <c r="AB58" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA58" t="inlineStr">
+      <c r="AC58" t="inlineStr">
         <is>
           <t>056</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr"/>
-      <c r="AC58" t="inlineStr">
+      <c r="AD58" t="inlineStr"/>
+      <c r="AE58" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/a614068b-94a2-069e-6cc9-c9c27c2a37e7/manifest</t>
         </is>
       </c>
-      <c r="AD58" t="inlineStr"/>
-      <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="inlineStr"/>
-      <c r="AH58" t="n">
+      <c r="AH58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr"/>
+      <c r="AJ58" t="n">
         <v>50</v>
       </c>
     </row>
@@ -7440,73 +7572,75 @@
         </is>
       </c>
       <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/67adb7ee-13a9-8527-98dd-582ab6d1815e.json</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>67adb7ee-13a9-8527-98dd-582ab6d1815e</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/67adb7ee-13a9-8527-98dd-582ab6d1815e</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="V59" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="W59" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/a5564ba6c799b80eaf9957eb0e2e966e4ee5a8bf.jpg</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249176</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr">
+      <c r="Y59" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="Z59" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr">
+      <c r="AA59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA59" t="inlineStr">
+      <c r="AC59" t="inlineStr">
         <is>
           <t>057</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr"/>
-      <c r="AC59" t="inlineStr">
+      <c r="AD59" t="inlineStr"/>
+      <c r="AE59" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/67adb7ee-13a9-8527-98dd-582ab6d1815e/manifest</t>
         </is>
       </c>
-      <c r="AD59" t="inlineStr"/>
-      <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="inlineStr"/>
-      <c r="AH59" t="n">
+      <c r="AH59" t="inlineStr"/>
+      <c r="AI59" t="inlineStr"/>
+      <c r="AJ59" t="n">
         <v>85</v>
       </c>
     </row>
@@ -7562,73 +7696,75 @@
         </is>
       </c>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/69cda5ec-59a8-75d3-9302-903deddd1b1b.json</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>69cda5ec-59a8-75d3-9302-903deddd1b1b</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/69cda5ec-59a8-75d3-9302-903deddd1b1b</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="V60" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="W60" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/5bbd2a3e2b4b04e446d48a8241dc2e1bf15460f3.jpg</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249177</t>
         </is>
       </c>
-      <c r="W60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="Z60" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr">
+      <c r="AA60" t="inlineStr"/>
+      <c r="AB60" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA60" t="inlineStr">
+      <c r="AC60" t="inlineStr">
         <is>
           <t>058</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr"/>
-      <c r="AC60" t="inlineStr">
+      <c r="AD60" t="inlineStr"/>
+      <c r="AE60" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/69cda5ec-59a8-75d3-9302-903deddd1b1b/manifest</t>
         </is>
       </c>
-      <c r="AD60" t="inlineStr"/>
-      <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="inlineStr"/>
-      <c r="AH60" t="n">
+      <c r="AH60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr"/>
+      <c r="AJ60" t="n">
         <v>182</v>
       </c>
     </row>
@@ -7684,73 +7820,75 @@
         </is>
       </c>
       <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4b5c431e-9ef6-3488-98b7-52829fe7a21f.json</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>4b5c431e-9ef6-3488-98b7-52829fe7a21f</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/4b5c431e-9ef6-3488-98b7-52829fe7a21f</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="V61" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="W61" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/94bb24db808b24eeb9166bb9d50279f6ccfe51f1.jpg</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249178</t>
         </is>
       </c>
-      <c r="W61" t="inlineStr">
+      <c r="Y61" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="Z61" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr">
+      <c r="AA61" t="inlineStr"/>
+      <c r="AB61" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA61" t="inlineStr">
+      <c r="AC61" t="inlineStr">
         <is>
           <t>059</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr"/>
-      <c r="AC61" t="inlineStr">
+      <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4b5c431e-9ef6-3488-98b7-52829fe7a21f/manifest</t>
         </is>
       </c>
-      <c r="AD61" t="inlineStr"/>
-      <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="inlineStr"/>
-      <c r="AH61" t="n">
+      <c r="AH61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr"/>
+      <c r="AJ61" t="n">
         <v>101</v>
       </c>
     </row>
@@ -7806,73 +7944,75 @@
         </is>
       </c>
       <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/84b46f92-0a4f-19b2-7e7e-3601f1cb0c75.json</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>84b46f92-0a4f-19b2-7e7e-3601f1cb0c75</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/84b46f92-0a4f-19b2-7e7e-3601f1cb0c75</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="V62" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="W62" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/975b0f324e47da401ca09a5d855a7cc0ed27315c.jpg</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249179</t>
         </is>
       </c>
-      <c r="W62" t="inlineStr">
+      <c r="Y62" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="Z62" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr">
+      <c r="AA62" t="inlineStr"/>
+      <c r="AB62" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA62" t="inlineStr">
+      <c r="AC62" t="inlineStr">
         <is>
           <t>060</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr"/>
-      <c r="AC62" t="inlineStr">
+      <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/84b46f92-0a4f-19b2-7e7e-3601f1cb0c75/manifest</t>
         </is>
       </c>
-      <c r="AD62" t="inlineStr"/>
-      <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="inlineStr"/>
-      <c r="AH62" t="n">
+      <c r="AH62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr"/>
+      <c r="AJ62" t="n">
         <v>97</v>
       </c>
     </row>
@@ -7928,73 +8068,75 @@
         </is>
       </c>
       <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/738079d0-9eac-9d25-9169-d5de6bd2a600.json</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>738079d0-9eac-9d25-9169-d5de6bd2a600</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/738079d0-9eac-9d25-9169-d5de6bd2a600</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="V63" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="W63" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/18550641df2cb8c1a89b23c27b5e875eb945b3e8.jpg</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249180</t>
         </is>
       </c>
-      <c r="W63" t="inlineStr">
+      <c r="Y63" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
+      <c r="Z63" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr">
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA63" t="inlineStr">
+      <c r="AC63" t="inlineStr">
         <is>
           <t>061</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr"/>
-      <c r="AC63" t="inlineStr">
+      <c r="AD63" t="inlineStr"/>
+      <c r="AE63" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/738079d0-9eac-9d25-9169-d5de6bd2a600/manifest</t>
         </is>
       </c>
-      <c r="AD63" t="inlineStr"/>
-      <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="inlineStr"/>
-      <c r="AH63" t="n">
+      <c r="AH63" t="inlineStr"/>
+      <c r="AI63" t="inlineStr"/>
+      <c r="AJ63" t="n">
         <v>86</v>
       </c>
     </row>
@@ -8050,74 +8192,2524 @@
         </is>
       </c>
       <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr">
         <is>
           <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9f410855-9663-1ee3-a296-481ef7d57da6.json</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>9f410855-9663-1ee3-a296-481ef7d57da6</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/9f410855-9663-1ee3-a296-481ef7d57da6</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="V64" t="inlineStr">
         <is>
           <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="W64" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/62aa4fd87a6deb93694cb03b7e0b0f53629a05ce.jpg</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1249181</t>
         </is>
       </c>
-      <c r="W64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo, JAPAN</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="Z64" t="inlineStr">
         <is>
           <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
         </is>
       </c>
-      <c r="Y64" t="inlineStr"/>
-      <c r="Z64" t="inlineStr">
+      <c r="AA64" t="inlineStr"/>
+      <c r="AB64" t="inlineStr">
         <is>
           <t>農学生命科学図書館コレクション|University Library for Agricultural and Life Sciences, the University of Tokyo Collection</t>
         </is>
       </c>
-      <c r="AA64" t="inlineStr">
+      <c r="AC64" t="inlineStr">
         <is>
           <t>062</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr"/>
-      <c r="AC64" t="inlineStr">
+      <c r="AD64" t="inlineStr"/>
+      <c r="AE64" t="inlineStr">
         <is>
           <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9f410855-9663-1ee3-a296-481ef7d57da6/manifest</t>
         </is>
       </c>
-      <c r="AD64" t="inlineStr"/>
-      <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="inlineStr"/>
-      <c r="AH64" t="n">
+      <c r="AH64" t="inlineStr"/>
+      <c r="AI64" t="inlineStr"/>
+      <c r="AJ64" t="n">
         <v>59</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>興業意見 第1回 : 巻1</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>コウギョウ イケン</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>[農商務省]</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>農商務省</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1884.12</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>600:6:1</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>第1回 : 巻1</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>図書</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/73566f00-08a6-61a8-65cb-6a764f911e81.json</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>73566f00-08a6-61a8-65cb-6a764f911e81</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/73566f00-08a6-61a8-65cb-6a764f911e81</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4a976e9ceb404caa70531f2c1342be862cd5ec60.jpg</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1404820</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr"/>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>063</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr"/>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/73566f00-08a6-61a8-65cb-6a764f911e81/manifest</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
+      <c r="AH65" t="inlineStr"/>
+      <c r="AI65" t="inlineStr"/>
+      <c r="AJ65" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>興業意見 第1回 : 巻2</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>コウギョウ イケン</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>[農商務省]</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>農商務省</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>1884.12</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>600:6:2</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>第1回 : 巻2</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>図書</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/927cc17e-1752-1ca0-5683-1f92514c4be8.json</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>927cc17e-1752-1ca0-5683-1f92514c4be8</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/927cc17e-1752-1ca0-5683-1f92514c4be8</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/21ef0290e79b11648fbe88e5ae707c725523b19b.jpg</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1404819</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr"/>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>064</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr"/>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/927cc17e-1752-1ca0-5683-1f92514c4be8/manifest</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="inlineStr"/>
+      <c r="AH66" t="inlineStr"/>
+      <c r="AI66" t="inlineStr"/>
+      <c r="AJ66" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>興業意見 第1回 : 巻3</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>コウギョウ イケン</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>[農商務省]</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>農商務省</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1884.12</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>600:6:3</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>第1回 : 巻3</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>図書</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4830573b-5fc4-13da-3cc6-3993b9932b0a.json</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>4830573b-5fc4-13da-3cc6-3993b9932b0a</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/4830573b-5fc4-13da-3cc6-3993b9932b0a</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/1592c1b365ffa1df68b6a094385d6fef551206a5.jpg</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1404818</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr"/>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>065</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr"/>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4830573b-5fc4-13da-3cc6-3993b9932b0a/manifest</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="inlineStr"/>
+      <c r="AH67" t="inlineStr"/>
+      <c r="AI67" t="inlineStr"/>
+      <c r="AJ67" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>興業意見 第1回 : 巻4</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>コウギョウ イケン</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>[農商務省]</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>農商務省</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>1884.12</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>600:6:4</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>第1回 : 巻4</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>図書</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/02279195-9d10-4ca0-3415-dd987fde41e6.json</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>02279195-9d10-4ca0-3415-dd987fde41e6</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/02279195-9d10-4ca0-3415-dd987fde41e6</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/21c20aa85bc5d856ad18d537ab4b3b888df030ae.jpg</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1404817</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr"/>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>066</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr"/>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/02279195-9d10-4ca0-3415-dd987fde41e6/manifest</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="inlineStr"/>
+      <c r="AH68" t="inlineStr"/>
+      <c r="AI68" t="inlineStr"/>
+      <c r="AJ68" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>興業意見 第1回 : 巻5</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>コウギョウ イケン</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>[農商務省]</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>農商務省</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1884.12</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>600:6:5</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>第1回 : 巻5</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>図書</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/735fdd6b-213f-758b-5994-dbf108570905.json</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>735fdd6b-213f-758b-5994-dbf108570905</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/735fdd6b-213f-758b-5994-dbf108570905</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/afc844102f271336a87ac173d9f5deb8a5e1aee6.jpg</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1404816</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr"/>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>067</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr"/>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/735fdd6b-213f-758b-5994-dbf108570905/manifest</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr"/>
+      <c r="AH69" t="inlineStr"/>
+      <c r="AI69" t="inlineStr"/>
+      <c r="AJ69" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>興業意見 第1回 : 巻6</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>コウギョウ イケン</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>[農商務省]</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>農商務省</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1884.12</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>600:6:6</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>第1回 : 巻6</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>図書</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/9a00871f-7576-5fa2-2410-3f1d59a68940.json</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>9a00871f-7576-5fa2-2410-3f1d59a68940</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/9a00871f-7576-5fa2-2410-3f1d59a68940</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/e2cdd5f86dc2eddb38e2307da8a06397ac5c2107.jpg</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1404815</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr"/>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>068</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr"/>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/9a00871f-7576-5fa2-2410-3f1d59a68940/manifest</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="inlineStr"/>
+      <c r="AH70" t="inlineStr"/>
+      <c r="AI70" t="inlineStr"/>
+      <c r="AJ70" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>興業意見 第1回 : 巻7</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>コウギョウ イケン</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>[農商務省]</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>農商務省</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1884.12</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>600:6:7</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>第1回 : 巻7</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>図書</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/81d903b2-0eef-75f7-7496-285add287853.json</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>81d903b2-0eef-75f7-7496-285add287853</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/81d903b2-0eef-75f7-7496-285add287853</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/4e92c65e06ae55427bffd9e9e853805b3ac8d32e.jpg</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1404814</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr"/>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>069</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr"/>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/81d903b2-0eef-75f7-7496-285add287853/manifest</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="inlineStr"/>
+      <c r="AH71" t="inlineStr"/>
+      <c r="AI71" t="inlineStr"/>
+      <c r="AJ71" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>興業意見 第1回 : 巻8</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>コウギョウ イケン</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>[農商務省]</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>農商務省</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1884.12</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>600:6:8</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>第1回 : 巻8</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>図書</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ebf626dc-431a-6452-1464-b89d4ed8117b.json</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>ebf626dc-431a-6452-1464-b89d4ed8117b</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/ebf626dc-431a-6452-1464-b89d4ed8117b</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/66746c40e099d1863caf302146b704b75d570796.jpg</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1404813</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr"/>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>070</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr"/>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ebf626dc-431a-6452-1464-b89d4ed8117b/manifest</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="inlineStr"/>
+      <c r="AH72" t="inlineStr"/>
+      <c r="AI72" t="inlineStr"/>
+      <c r="AJ72" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>興業意見 第1回 : 巻9</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>コウギョウ イケン</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>[農商務省]</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>農商務省</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>1884.12</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>600:6:9</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>第1回 : 巻9</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>図書</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/1c09a943-450d-22d3-3a08-4c836ba171f1.json</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>1c09a943-450d-22d3-3a08-4c836ba171f1</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/1c09a943-450d-22d3-3a08-4c836ba171f1</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/0e51f7fea13da099bd4fc8c3b59c81ea059cfc95.jpg</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1404812</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>071</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr"/>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/1c09a943-450d-22d3-3a08-4c836ba171f1/manifest</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="inlineStr"/>
+      <c r="AH73" t="inlineStr"/>
+      <c r="AI73" t="inlineStr"/>
+      <c r="AJ73" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>興業意見 第1回 : 巻10</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>コウギョウ イケン</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>[農商務省]</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>農商務省</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1884.12</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>600:6:10</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>第1回 : 巻10</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>図書</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b34d4cb4-1972-8bec-3dc3-d69abe7d6940.json</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>b34d4cb4-1972-8bec-3dc3-d69abe7d6940</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/b34d4cb4-1972-8bec-3dc3-d69abe7d6940</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/9d95639717e4e1fcc18c62b8bc2014799930e274.jpg</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1404811</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>072</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr"/>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b34d4cb4-1972-8bec-3dc3-d69abe7d6940/manifest</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="inlineStr"/>
+      <c r="AH74" t="inlineStr"/>
+      <c r="AI74" t="inlineStr"/>
+      <c r="AJ74" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>興業意見 第1回 : 巻11</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>コウギョウ イケン</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>[農商務省]</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>農商務省</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>1884.12</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>600:6:11</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>第1回 : 巻11</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>図書</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/af7bf8d2-455f-6a38-27f0-90e8933d7e29.json</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>af7bf8d2-455f-6a38-27f0-90e8933d7e29</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/af7bf8d2-455f-6a38-27f0-90e8933d7e29</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/fbdb784f79c0d7e32404e904c009805658f6a0fa.jpg</t>
+        </is>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1404810</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>073</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr"/>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/af7bf8d2-455f-6a38-27f0-90e8933d7e29/manifest</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="inlineStr"/>
+      <c r="AH75" t="inlineStr"/>
+      <c r="AI75" t="inlineStr"/>
+      <c r="AJ75" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>興業意見 第1回 : 巻12</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>コウギョウ イケン</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>[農商務省]</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>農商務省</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>1884.12</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>600:6:12</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>第1回 : 巻12</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>図書</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/bb2d215a-042f-8f08-0539-857ea4056c4d.json</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>bb2d215a-042f-8f08-0539-857ea4056c4d</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/bb2d215a-042f-8f08-0539-857ea4056c4d</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f9fb08a950e90570934144d4128dbcdd9a5ec958.jpg</t>
+        </is>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1404809</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>074</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr"/>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/bb2d215a-042f-8f08-0539-857ea4056c4d/manifest</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="inlineStr"/>
+      <c r="AH76" t="inlineStr"/>
+      <c r="AI76" t="inlineStr"/>
+      <c r="AJ76" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>興業意見 第1回 : 巻13</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>コウギョウ イケン</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>[農商務省]</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>農商務省</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1884.12</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>600:6:13</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>第1回 : 巻13</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>図書</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/ace4022b-645d-2a28-9cff-5200d4053dbc.json</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>ace4022b-645d-2a28-9cff-5200d4053dbc</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/ace4022b-645d-2a28-9cff-5200d4053dbc</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b2fa63cd123bf3e8669bc0cc7ae8b62783317841.jpg</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1404808</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>075</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr"/>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/ace4022b-645d-2a28-9cff-5200d4053dbc/manifest</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="inlineStr"/>
+      <c r="AH77" t="inlineStr"/>
+      <c r="AI77" t="inlineStr"/>
+      <c r="AJ77" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>興業意見 第1回 : 巻14</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>コウギョウ イケン</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>[農商務省]</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>農商務省</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>1884.12</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>600:6:14</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>第1回 : 巻14</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>図書</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/f3a3b864-5958-3735-9e1e-531ac72e9a60.json</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>f3a3b864-5958-3735-9e1e-531ac72e9a60</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/f3a3b864-5958-3735-9e1e-531ac72e9a60</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/45eb1cb54311f74fc5cac3361525c54130f78528.jpg</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1404807</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>076</t>
+        </is>
+      </c>
+      <c r="AD78" t="inlineStr"/>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/f3a3b864-5958-3735-9e1e-531ac72e9a60/manifest</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="inlineStr"/>
+      <c r="AH78" t="inlineStr"/>
+      <c r="AI78" t="inlineStr"/>
+      <c r="AJ78" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>興業意見 第1回 : 巻15</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>コウギョウ イケン</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>[農商務省]</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>農商務省</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>1884.12</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>600:6:15</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>第1回 : 巻15</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>図書</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/47f33571-01d0-8169-6d7e-1a8505502213.json</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>47f33571-01d0-8169-6d7e-1a8505502213</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/47f33571-01d0-8169-6d7e-1a8505502213</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/fd933ca0df2937d935c4ecf6a70bdaf732df8dc5.jpg</t>
+        </is>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1404806</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>077</t>
+        </is>
+      </c>
+      <c r="AD79" t="inlineStr"/>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/47f33571-01d0-8169-6d7e-1a8505502213/manifest</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="inlineStr"/>
+      <c r="AH79" t="inlineStr"/>
+      <c r="AI79" t="inlineStr"/>
+      <c r="AJ79" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>興業意見 第1回 : 巻16</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>コウギョウ イケン</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>[農商務省]</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>農商務省</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1884.12</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>600:6:16</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>第1回 : 巻16</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>図書</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/aea62ba8-69c7-9d8f-2289-7dc6f5404644.json</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>aea62ba8-69c7-9d8f-2289-7dc6f5404644</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/aea62ba8-69c7-9d8f-2289-7dc6f5404644</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/f80e1e750083a6c667a10cba2535eb8fbcbddccd.jpg</t>
+        </is>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1404805</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>078</t>
+        </is>
+      </c>
+      <c r="AD80" t="inlineStr"/>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/aea62ba8-69c7-9d8f-2289-7dc6f5404644/manifest</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr"/>
+      <c r="AH80" t="inlineStr"/>
+      <c r="AI80" t="inlineStr"/>
+      <c r="AJ80" t="n">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>興業意見 第1回 : 巻17</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>コウギョウ イケン</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>[農商務省]</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>農商務省</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1884.12</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>600:6:17</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>第1回 : 巻17</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>図書</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/b5f3ce8a-3e0a-8b0a-684e-e014e23a9d37.json</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>b5f3ce8a-3e0a-8b0a-684e-e014e23a9d37</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/b5f3ce8a-3e0a-8b0a-684e-e014e23a9d37</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/b148bf6868a988981749120ad5f4e4407071170e.jpg</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1404804</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>079</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/b5f3ce8a-3e0a-8b0a-684e-e014e23a9d37/manifest</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr"/>
+      <c r="AH81" t="inlineStr"/>
+      <c r="AI81" t="inlineStr"/>
+      <c r="AJ81" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>興業意見 第1回 : 巻18</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>コウギョウ イケン</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>[農商務省]</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>農商務省</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>1884.12</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1冊</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>600:6:18</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Agri. Library, UTokyo Collection</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>第1回 : 巻18</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>図書</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>日本語</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>http://tify.sub.uni-goettingen.de/demo.html?manifest=https://archdataset.dl.itc.u-tokyo.ac.jp/manifest/4727a812-1dcd-89cc-8a3d-75bd442217e5.json</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>4727a812-1dcd-89cc-8a3d-75bd442217e5</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/s/agriculture/document/4727a812-1dcd-89cc-8a3d-75bd442217e5</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>https://www.lib.u-tokyo.ac.jp/ja/library/contents/archives-top/reuse</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/files/medium/7f883c6b41962e53777629a79ceb2b4a2b969b12.jpg</t>
+        </is>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/api/items/1404803</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>東京大学農学生命科学研究科・農学部 / Graduate School of Agricultural and Life Sciences/Faculty of Agriculture, The University of Tokyo</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>http://iiif.io/api/presentation/2#rightToLeftDirection</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr"/>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>農学生命科学図書館コレクション</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>080</t>
+        </is>
+      </c>
+      <c r="AD82" t="inlineStr"/>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>https://iiif.dl.itc.u-tokyo.ac.jp/repo/iiif/4727a812-1dcd-89cc-8a3d-75bd442217e5/manifest</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="inlineStr"/>
+      <c r="AH82" t="inlineStr"/>
+      <c r="AI82" t="inlineStr"/>
+      <c r="AJ82" t="n">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
